--- a/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
+++ b/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
@@ -7346,7 +7346,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7564,7 +7564,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7685,7 +7685,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7806,7 +7806,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7927,7 +7927,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8048,7 +8048,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
+++ b/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
@@ -5887,7 +5887,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5906,7 +5906,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
+++ b/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
@@ -6200,7 +6200,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6219,6 +6219,347 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經橋接表；唯讀）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">itpg_vr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架未另訂（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：同 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">vr26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年部署中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">世代占比（混合用）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">quanta/dist/20261025_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
@@ -6238,7 +6579,237 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E10</t>
+      <t xml:space="preserve">In!D11:F11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達模型輸入（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TrendForce 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin 22%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；鴻海：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Vera </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相關產品 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逐步放量（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法說）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">racks_gb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">架</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晶片內容橋接表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E6</t>
     </r>
     <r>
       <rPr>
@@ -6276,7 +6847,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">H10</t>
+      <t xml:space="preserve">H6</t>
     </r>
     <r>
       <rPr>
@@ -6316,20 +6887,20 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Tokenomics v20.1 IF_CapexIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經橋接表；唯讀）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">itpg_vr</t>
+      <t xml:space="preserve">Tokenomics IF_RacksPerGW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（經橋接表）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">racks_vr</t>
   </si>
   <si>
     <r>
@@ -6349,16 +6920,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GW IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資本支出（</t>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機架數（</t>
     </r>
     <r>
       <rPr>
@@ -6377,367 +6948,21 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin Ultra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架未另訂（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：同 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">vr26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年部署中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">世代占比（混合用）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!D11:F11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型輸入（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TrendForce 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin 22%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；鴻海：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Vera </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相關產品 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逐步放量（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法說）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">racks_gb</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架數（</t>
+    <t xml:space="preserve">rack_gb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整櫃買方價格（</t>
     </r>
     <r>
       <rPr>
@@ -6756,22 +6981,59 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">架</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">US$M/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">架</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6790,269 +7052,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tokenomics IF_RacksPerGW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（經橋接表）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">racks_vr</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機架數（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VR200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">rack_gb</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">整櫃買方價格（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tokenomics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">US$M/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">架</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晶片內容橋接表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -38905,7 +38905,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>33</v>
@@ -41921,7 +41921,7 @@
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">PL!D67</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">PL!E67</f>
@@ -42037,11 +42037,11 @@
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">PL!F74/fx</f>
-        <v>201.698052189861</v>
+        <v>201.698052189862</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">PL!G74/fx</f>
-        <v>204.635316604915</v>
+        <v>204.635316604916</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42057,11 +42057,11 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">PL!E86</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">PL!F86</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">PL!G86</f>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">PL!E85</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">PL!F85</f>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="F12" s="16" t="n">
         <f aca="false">PL!G85</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42139,7 +42139,7 @@
         <v>0.127201317776965</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>422</v>
@@ -42166,7 +42166,7 @@
       </c>
       <c r="F15" s="15" t="n">
         <f aca="false">F7+F14</f>
-        <v>0.286386066269603</v>
+        <v>0.286386066269604</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>424</v>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">C6*(1-C15)</f>
-        <v>438.833408472511</v>
+        <v>438.83340847251</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">D6*(1-D15)</f>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="E6" s="15" t="n">
         <f aca="false">E82</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">F82</f>
@@ -42333,15 +42333,15 @@
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">E74</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">F74</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">G74</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42389,11 +42389,11 @@
       </c>
       <c r="E9" s="15" t="n">
         <f aca="false">E83</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">F83</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">G83</f>
@@ -42421,7 +42421,7 @@
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">F90</f>
-        <v>954.148080267576</v>
+        <v>954.148080267577</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">G90</f>
@@ -42501,7 +42501,7 @@
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E98</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">F98</f>
@@ -42509,7 +42509,7 @@
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">G98</f>
-        <v>471.817290313208</v>
+        <v>471.817290313209</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42537,7 +42537,7 @@
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">G100</f>
-        <v>33.6604474903365</v>
+        <v>33.6604474903366</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42553,15 +42553,15 @@
       </c>
       <c r="E15" s="15" t="n">
         <f aca="false">E101</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F15" s="15" t="n">
         <f aca="false">F101</f>
-        <v>0.176034728479648</v>
+        <v>0.176034728479647</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G101</f>
-        <v>0.0713949219242656</v>
+        <v>0.0713949219242658</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="E19" s="15" t="n">
         <f aca="false">E126</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">F126</f>
@@ -42638,15 +42638,15 @@
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">E118</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F20" s="19" t="n">
         <f aca="false">F118</f>
-        <v>5163.47013606045</v>
+        <v>5163.47013606046</v>
       </c>
       <c r="G20" s="19" t="n">
         <f aca="false">G118</f>
-        <v>5566.0806116537</v>
+        <v>5566.08061165371</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42694,7 +42694,7 @@
       </c>
       <c r="E22" s="15" t="n">
         <f aca="false">E127</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F22" s="15" t="n">
         <f aca="false">F127</f>
@@ -42726,11 +42726,11 @@
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">F134</f>
-        <v>866.86131618284</v>
+        <v>866.861316182841</v>
       </c>
       <c r="G23" s="19" t="n">
         <f aca="false">G134</f>
-        <v>934.156609281438</v>
+        <v>934.156609281439</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42806,15 +42806,15 @@
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">E142</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F26" s="19" t="n">
         <f aca="false">F142</f>
-        <v>388.349774586782</v>
+        <v>388.349774586783</v>
       </c>
       <c r="G26" s="19" t="n">
         <f aca="false">G142</f>
-        <v>429.078027379191</v>
+        <v>429.078027379192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="E28" s="15" t="n">
         <f aca="false">E145</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F28" s="15" t="n">
         <f aca="false">F145</f>
@@ -42915,7 +42915,7 @@
       </c>
       <c r="E32" s="15" t="n">
         <f aca="false">E170</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F32" s="15" t="n">
         <f aca="false">F170</f>
@@ -42943,7 +42943,7 @@
       </c>
       <c r="E33" s="19" t="n">
         <f aca="false">E162</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F33" s="19" t="n">
         <f aca="false">F162</f>
@@ -42999,7 +42999,7 @@
       </c>
       <c r="E35" s="15" t="n">
         <f aca="false">E171</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F35" s="15" t="n">
         <f aca="false">F171</f>
@@ -43035,7 +43035,7 @@
       </c>
       <c r="G36" s="19" t="n">
         <f aca="false">G178</f>
-        <v>816.681852736461</v>
+        <v>816.681852736462</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43111,7 +43111,7 @@
       </c>
       <c r="E39" s="19" t="n">
         <f aca="false">E186</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F39" s="19" t="n">
         <f aca="false">F186</f>
@@ -43119,7 +43119,7 @@
       </c>
       <c r="G39" s="19" t="n">
         <f aca="false">G186</f>
-        <v>353.241276810965</v>
+        <v>353.241276810966</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43163,15 +43163,15 @@
       </c>
       <c r="E41" s="15" t="n">
         <f aca="false">E189</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F41" s="15" t="n">
         <f aca="false">F189</f>
-        <v>-0.116750764152285</v>
+        <v>-0.116750764152286</v>
       </c>
       <c r="G41" s="15" t="n">
         <f aca="false">G189</f>
-        <v>0.0680314803297637</v>
+        <v>0.0680314803297639</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43251,7 +43251,7 @@
       </c>
       <c r="D63" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -43350,7 +43350,7 @@
       </c>
       <c r="D67" s="19" t="n">
         <f aca="false">D65*D66</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E67" s="19" t="n">
         <f aca="false">E65*E66</f>
@@ -43374,7 +43374,7 @@
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">D67*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E68" s="19" t="n">
         <f aca="false">E67*fx</f>
@@ -43465,15 +43465,15 @@
       </c>
       <c r="E72" s="19" t="n">
         <f aca="false">E68*E71</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F72" s="19" t="n">
         <f aca="false">F68*F71</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G72" s="19" t="n">
         <f aca="false">G68*G71</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43520,15 +43520,15 @@
       </c>
       <c r="E74" s="19" t="n">
         <f aca="false">E72*(1-E73)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F74" s="19" t="n">
         <f aca="false">F72*(1-F73)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G74" s="19" t="n">
         <f aca="false">G72*(1-G73)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43717,7 +43717,7 @@
       </c>
       <c r="E82" s="15" t="n">
         <f aca="false">E81/D81-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F82" s="15" t="n">
         <f aca="false">F81/E81-1</f>
@@ -43745,11 +43745,11 @@
       </c>
       <c r="E83" s="15" t="n">
         <f aca="false">E74/E81</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F83" s="15" t="n">
         <f aca="false">F74/F81</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G83" s="15" t="n">
         <f aca="false">G74/G81</f>
@@ -43777,7 +43777,7 @@
       </c>
       <c r="F84" s="15" t="n">
         <f aca="false">(F74+F76)/F81</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G84" s="15" t="n">
         <f aca="false">(G74+G76)/G81</f>
@@ -43797,7 +43797,7 @@
       </c>
       <c r="E85" s="16" t="n">
         <f aca="false">E74/fx/E65</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F85" s="16" t="n">
         <f aca="false">F74/fx/F65</f>
@@ -43805,7 +43805,7 @@
       </c>
       <c r="G85" s="16" t="n">
         <f aca="false">G74/fx/G65</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43821,11 +43821,11 @@
       </c>
       <c r="E86" s="19" t="n">
         <f aca="false">E72/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F86" s="19" t="n">
         <f aca="false">F72/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G86" s="19" t="n">
         <f aca="false">G72/fx/odm_vr</f>
@@ -43872,11 +43872,11 @@
       </c>
       <c r="F89" s="22" t="n">
         <f aca="false">($D$88+d_ai+vrd)*F72*(1-F73*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G89" s="22" t="n">
         <f aca="false">($D$88+d_ai+vrd)*G72*(1-G73*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>472</v>
@@ -43903,7 +43903,7 @@
       </c>
       <c r="F90" s="19" t="n">
         <f aca="false">$D$88*F80+F89</f>
-        <v>954.148080267576</v>
+        <v>954.148080267577</v>
       </c>
       <c r="G90" s="19" t="n">
         <f aca="false">$D$88*G80+G89</f>
@@ -44038,15 +44038,15 @@
       </c>
       <c r="E95" s="19" t="n">
         <f aca="false">E90-E94</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F95" s="19" t="n">
         <f aca="false">F90-F94</f>
-        <v>667.237325531465</v>
+        <v>667.237325531466</v>
       </c>
       <c r="G95" s="19" t="n">
         <f aca="false">G90-G94</f>
-        <v>714.87468229274</v>
+        <v>714.874682292741</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44122,7 +44122,7 @@
       </c>
       <c r="E98" s="19" t="n">
         <f aca="false">E95*E97</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F98" s="19" t="n">
         <f aca="false">F95*F97</f>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="G98" s="19" t="n">
         <f aca="false">G95*G97</f>
-        <v>471.817290313208</v>
+        <v>471.817290313209</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44186,7 +44186,7 @@
       </c>
       <c r="G100" s="22" t="n">
         <f aca="false">G98/G99</f>
-        <v>33.6604474903365</v>
+        <v>33.6604474903366</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44202,15 +44202,15 @@
       </c>
       <c r="E101" s="15" t="n">
         <f aca="false">E100/D100-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F101" s="15" t="n">
         <f aca="false">F100/E100-1</f>
-        <v>0.176034728479648</v>
+        <v>0.176034728479647</v>
       </c>
       <c r="G101" s="15" t="n">
         <f aca="false">G100/F100-1</f>
-        <v>0.0713949219242656</v>
+        <v>0.0713949219242658</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44258,7 +44258,7 @@
       </c>
       <c r="D107" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E107" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -44357,7 +44357,7 @@
       </c>
       <c r="D111" s="19" t="n">
         <f aca="false">D109*D110</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E111" s="19" t="n">
         <f aca="false">E109*E110</f>
@@ -44381,7 +44381,7 @@
       </c>
       <c r="D112" s="19" t="n">
         <f aca="false">D111*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E112" s="19" t="n">
         <f aca="false">E111*fx</f>
@@ -44472,15 +44472,15 @@
       </c>
       <c r="E116" s="19" t="n">
         <f aca="false">E112*E115</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F116" s="19" t="n">
         <f aca="false">F112*F115</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G116" s="19" t="n">
         <f aca="false">G112*G115</f>
-        <v>7421.44081553827</v>
+        <v>7421.44081553828</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44527,15 +44527,15 @@
       </c>
       <c r="E118" s="19" t="n">
         <f aca="false">E116*(1-E117)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F118" s="19" t="n">
         <f aca="false">F116*(1-F117)</f>
-        <v>5163.47013606045</v>
+        <v>5163.47013606046</v>
       </c>
       <c r="G118" s="19" t="n">
         <f aca="false">G116*(1-G117)</f>
-        <v>5566.0806116537</v>
+        <v>5566.08061165371</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="E126" s="15" t="n">
         <f aca="false">E125/D125-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F126" s="15" t="n">
         <f aca="false">F125/E125-1</f>
@@ -44752,7 +44752,7 @@
       </c>
       <c r="E127" s="15" t="n">
         <f aca="false">E118/E125</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F127" s="15" t="n">
         <f aca="false">F118/F125</f>
@@ -44804,7 +44804,7 @@
       </c>
       <c r="E129" s="16" t="n">
         <f aca="false">E118/fx/E109</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F129" s="16" t="n">
         <f aca="false">F118/fx/F109</f>
@@ -44812,7 +44812,7 @@
       </c>
       <c r="G129" s="16" t="n">
         <f aca="false">G118/fx/G109</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="E130" s="19" t="n">
         <f aca="false">E116/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F130" s="19" t="n">
         <f aca="false">F116/fx/odm_vr</f>
@@ -44836,7 +44836,7 @@
       </c>
       <c r="G130" s="19" t="n">
         <f aca="false">G116/fx/odm_vr</f>
-        <v>34.3585222941586</v>
+        <v>34.3585222941587</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>467</v>
@@ -44883,7 +44883,7 @@
       </c>
       <c r="G133" s="22" t="n">
         <f aca="false">($D$132+d_ai+vrd)*G116*(1-G117*(1-keep))</f>
-        <v>399.414172252921</v>
+        <v>399.414172252922</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>472</v>
@@ -44910,11 +44910,11 @@
       </c>
       <c r="F134" s="19" t="n">
         <f aca="false">$D$132*F124+F133</f>
-        <v>866.86131618284</v>
+        <v>866.861316182841</v>
       </c>
       <c r="G134" s="19" t="n">
         <f aca="false">$D$132*G124+G133</f>
-        <v>934.156609281438</v>
+        <v>934.156609281439</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45045,7 +45045,7 @@
       </c>
       <c r="E139" s="19" t="n">
         <f aca="false">E134-E138</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F139" s="19" t="n">
         <f aca="false">F134-F138</f>
@@ -45129,15 +45129,15 @@
       </c>
       <c r="E142" s="19" t="n">
         <f aca="false">E139*E141</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F142" s="19" t="n">
         <f aca="false">F139*F141</f>
-        <v>388.349774586782</v>
+        <v>388.349774586783</v>
       </c>
       <c r="G142" s="19" t="n">
         <f aca="false">G139*G141</f>
-        <v>429.078027379191</v>
+        <v>429.078027379192</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45209,7 +45209,7 @@
       </c>
       <c r="E145" s="15" t="n">
         <f aca="false">E144/D144-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F145" s="15" t="n">
         <f aca="false">F144/E144-1</f>
@@ -45265,7 +45265,7 @@
       </c>
       <c r="D151" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E151" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -45364,7 +45364,7 @@
       </c>
       <c r="D155" s="19" t="n">
         <f aca="false">D153*D154</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E155" s="19" t="n">
         <f aca="false">E153*E154</f>
@@ -45388,7 +45388,7 @@
       </c>
       <c r="D156" s="19" t="n">
         <f aca="false">D155*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E156" s="19" t="n">
         <f aca="false">E155*fx</f>
@@ -45479,15 +45479,15 @@
       </c>
       <c r="E160" s="19" t="n">
         <f aca="false">E156*E159</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F160" s="19" t="n">
         <f aca="false">F156*F159</f>
-        <v>4840.75325255667</v>
+        <v>4840.75325255668</v>
       </c>
       <c r="G160" s="19" t="n">
         <f aca="false">G156*G159</f>
-        <v>5238.66410508583</v>
+        <v>5238.66410508584</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45534,7 +45534,7 @@
       </c>
       <c r="E162" s="19" t="n">
         <f aca="false">E160*(1-E161)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F162" s="19" t="n">
         <f aca="false">F160*(1-F161)</f>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="E170" s="15" t="n">
         <f aca="false">E169/D169-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F170" s="15" t="n">
         <f aca="false">F169/E169-1</f>
@@ -45759,7 +45759,7 @@
       </c>
       <c r="E171" s="15" t="n">
         <f aca="false">E162/E169</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F171" s="15" t="n">
         <f aca="false">F162/F169</f>
@@ -45795,7 +45795,7 @@
       </c>
       <c r="G172" s="15" t="n">
         <f aca="false">(G162+G164)/G169</f>
-        <v>0.555631753312207</v>
+        <v>0.555631753312208</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45811,7 +45811,7 @@
       </c>
       <c r="E173" s="16" t="n">
         <f aca="false">E162/fx/E153</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F173" s="16" t="n">
         <f aca="false">F162/fx/F153</f>
@@ -45819,7 +45819,7 @@
       </c>
       <c r="G173" s="16" t="n">
         <f aca="false">G162/fx/G153</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45835,7 +45835,7 @@
       </c>
       <c r="E174" s="19" t="n">
         <f aca="false">E160/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F174" s="19" t="n">
         <f aca="false">F160/fx/odm_vr</f>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="G177" s="22" t="n">
         <f aca="false">($D$176+d_ai+vrd)*G160*(1-G161*(1-keep))</f>
-        <v>281.939415707944</v>
+        <v>281.939415707945</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>472</v>
@@ -45921,7 +45921,7 @@
       </c>
       <c r="G178" s="19" t="n">
         <f aca="false">$D$176*G168+G177</f>
-        <v>816.681852736461</v>
+        <v>816.681852736462</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46052,7 +46052,7 @@
       </c>
       <c r="E183" s="19" t="n">
         <f aca="false">E178-E182</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F183" s="19" t="n">
         <f aca="false">F178-F182</f>
@@ -46136,7 +46136,7 @@
       </c>
       <c r="E186" s="19" t="n">
         <f aca="false">E183*E185</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F186" s="19" t="n">
         <f aca="false">F183*F185</f>
@@ -46144,7 +46144,7 @@
       </c>
       <c r="G186" s="19" t="n">
         <f aca="false">G183*G185</f>
-        <v>353.241276810965</v>
+        <v>353.241276810966</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46216,15 +46216,15 @@
       </c>
       <c r="E189" s="15" t="n">
         <f aca="false">E188/D188-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F189" s="15" t="n">
         <f aca="false">F188/E188-1</f>
-        <v>-0.116750764152285</v>
+        <v>-0.116750764152286</v>
       </c>
       <c r="G189" s="15" t="n">
         <f aca="false">G188/F188-1</f>
-        <v>0.0680314803297637</v>
+        <v>0.0680314803297639</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46329,7 +46329,7 @@
       </c>
       <c r="E196" s="15" t="n">
         <f aca="false">E195/D195-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F196" s="15" t="n">
         <f aca="false">F195/E195-1</f>
@@ -46369,7 +46369,7 @@
       </c>
       <c r="E197" s="19" t="n">
         <f aca="false">E98</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F197" s="19" t="n">
         <f aca="false">F98</f>
@@ -46377,7 +46377,7 @@
       </c>
       <c r="G197" s="19" t="n">
         <f aca="false">G98</f>
-        <v>471.817290313208</v>
+        <v>471.817290313209</v>
       </c>
       <c r="H197" s="24" t="n">
         <f aca="false">H195*H198</f>
@@ -46500,11 +46500,11 @@
       </c>
       <c r="G200" s="16" t="n">
         <f aca="false">G100</f>
-        <v>33.6604474903365</v>
+        <v>33.6604474903366</v>
       </c>
       <c r="H200" s="27" t="n">
         <f aca="false">H197/H199</f>
-        <v>34.8921060489596</v>
+        <v>34.8921060489597</v>
       </c>
       <c r="I200" s="27" t="n">
         <f aca="false">I197/I199</f>
@@ -46529,15 +46529,15 @@
       </c>
       <c r="E201" s="15" t="n">
         <f aca="false">E200/D200-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F201" s="15" t="n">
         <f aca="false">F200/E200-1</f>
-        <v>0.176034728479648</v>
+        <v>0.176034728479647</v>
       </c>
       <c r="G201" s="15" t="n">
         <f aca="false">G200/F200-1</f>
-        <v>0.0713949219242656</v>
+        <v>0.0713949219242658</v>
       </c>
       <c r="H201" s="25" t="n">
         <f aca="false">H200/G200-1</f>
@@ -46549,7 +46549,7 @@
       </c>
       <c r="J201" s="25" t="n">
         <f aca="false">J200/I200-1</f>
-        <v>0.0600000000000001</v>
+        <v>0.0600000000000003</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46679,7 +46679,7 @@
       </c>
       <c r="E208" s="15" t="n">
         <f aca="false">E207/D207-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F208" s="15" t="n">
         <f aca="false">F207/E207-1</f>
@@ -46719,15 +46719,15 @@
       </c>
       <c r="E209" s="19" t="n">
         <f aca="false">E142</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F209" s="19" t="n">
         <f aca="false">F142</f>
-        <v>388.349774586782</v>
+        <v>388.349774586783</v>
       </c>
       <c r="G209" s="19" t="n">
         <f aca="false">G142</f>
-        <v>429.078027379191</v>
+        <v>429.078027379192</v>
       </c>
       <c r="H209" s="24" t="n">
         <f aca="false">H207*H210</f>
@@ -46735,7 +46735,7 @@
       </c>
       <c r="I209" s="24" t="n">
         <f aca="false">I207*I210</f>
-        <v>437.388195535486</v>
+        <v>437.388195535487</v>
       </c>
       <c r="J209" s="24" t="n">
         <f aca="false">J207*J210</f>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="I210" s="25" t="n">
         <f aca="false">$G$210+($C$215-$G$210)*2/3</f>
-        <v>0.0282752411308896</v>
+        <v>0.0282752411308897</v>
       </c>
       <c r="J210" s="25" t="n">
         <f aca="false">$G$210+($C$215-$G$210)*3/3</f>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="E213" s="15" t="n">
         <f aca="false">E212/D212-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F213" s="15" t="n">
         <f aca="false">F212/E212-1</f>
@@ -47029,7 +47029,7 @@
       </c>
       <c r="E220" s="15" t="n">
         <f aca="false">E219/D219-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F220" s="15" t="n">
         <f aca="false">F219/E219-1</f>
@@ -47069,7 +47069,7 @@
       </c>
       <c r="E221" s="19" t="n">
         <f aca="false">E186</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F221" s="19" t="n">
         <f aca="false">F186</f>
@@ -47077,11 +47077,11 @@
       </c>
       <c r="G221" s="19" t="n">
         <f aca="false">G186</f>
-        <v>353.241276810965</v>
+        <v>353.241276810966</v>
       </c>
       <c r="H221" s="24" t="n">
         <f aca="false">H219*H222</f>
-        <v>337.839930786209</v>
+        <v>337.83993078621</v>
       </c>
       <c r="I221" s="24" t="n">
         <f aca="false">I219*I222</f>
@@ -47117,7 +47117,7 @@
       </c>
       <c r="G222" s="15" t="n">
         <f aca="false">G221/G219</f>
-        <v>0.0281999877847309</v>
+        <v>0.028199987784731</v>
       </c>
       <c r="H222" s="25" t="n">
         <f aca="false">$G$222+($C$227-$G$222)*1/3</f>
@@ -47229,19 +47229,19 @@
       </c>
       <c r="E225" s="15" t="n">
         <f aca="false">E224/D224-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F225" s="15" t="n">
         <f aca="false">F224/E224-1</f>
-        <v>-0.116750764152285</v>
+        <v>-0.116750764152286</v>
       </c>
       <c r="G225" s="15" t="n">
         <f aca="false">G224/F224-1</f>
-        <v>0.0680314803297637</v>
+        <v>0.0680314803297639</v>
       </c>
       <c r="H225" s="25" t="n">
         <f aca="false">H224/G224-1</f>
-        <v>-0.0436000746113198</v>
+        <v>-0.0436000746113197</v>
       </c>
       <c r="I225" s="25" t="n">
         <f aca="false">I224/H224-1</f>
@@ -47249,7 +47249,7 @@
       </c>
       <c r="J225" s="25" t="n">
         <f aca="false">J224/I224-1</f>
-        <v>-0.0584615384615386</v>
+        <v>-0.0584615384615383</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47375,15 +47375,15 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">px/PL!E14</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">px/PL!E27</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">px/PL!E40</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>512</v>
@@ -47395,7 +47395,7 @@
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">px/PL!F14</f>
-        <v>7.7982253785189</v>
+        <v>7.79822537851889</v>
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">px/PL!F27</f>
@@ -47438,7 +47438,7 @@
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">px/B11</f>
-        <v>9.684086204978</v>
+        <v>9.68408620497799</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47593,15 +47593,15 @@
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">C23*D23</f>
-        <v>265.009734572012</v>
+        <v>265.009734572013</v>
       </c>
       <c r="F23" s="32" t="n">
         <f aca="false">E23/px-1</f>
-        <v>0.0816723860082138</v>
+        <v>0.0816723860082151</v>
       </c>
       <c r="G23" s="30" t="n">
         <f aca="false">px/C23</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47622,15 +47622,15 @@
       </c>
       <c r="E24" s="31" t="n">
         <f aca="false">C24*D24</f>
-        <v>265.009734572012</v>
+        <v>265.009734572013</v>
       </c>
       <c r="F24" s="32" t="n">
         <f aca="false">E24/px-1</f>
-        <v>0.0816723860082138</v>
+        <v>0.0816723860082151</v>
       </c>
       <c r="G24" s="30" t="n">
         <f aca="false">px/C24</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47655,11 +47655,11 @@
       </c>
       <c r="F25" s="32" t="n">
         <f aca="false">E25/px-1</f>
-        <v>0.00861588413064296</v>
+        <v>0.00861588413064407</v>
       </c>
       <c r="G25" s="30" t="n">
         <f aca="false">px/C25</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47687,7 +47687,7 @@
       </c>
       <c r="B28" s="18" t="n">
         <f aca="false">px*A28/PL!F14</f>
-        <v>7.7982253785189</v>
+        <v>7.79822537851889</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">px*A28/PL!F40</f>
@@ -47704,7 +47704,7 @@
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">px*A29/PL!F14</f>
-        <v>8.57804791637079</v>
+        <v>8.57804791637078</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">px*A29/PL!F40</f>
@@ -47787,7 +47787,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">tp_wA*B40+tp_wB*B41+tp_wC*B42</f>
-        <v>261.429965980011</v>
+        <v>261.429965980012</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -47801,7 +47801,7 @@
       </c>
       <c r="B39" s="35" t="n">
         <f aca="false">B38/px-1</f>
-        <v>0.0670610856326999</v>
+        <v>0.067061085632701</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
@@ -47815,7 +47815,7 @@
       </c>
       <c r="B40" s="28" t="n">
         <f aca="false">E23</f>
-        <v>265.009734572012</v>
+        <v>265.009734572013</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>544</v>
@@ -47827,7 +47827,7 @@
       </c>
       <c r="B41" s="28" t="n">
         <f aca="false">E24</f>
-        <v>265.009734572012</v>
+        <v>265.009734572013</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>546</v>
@@ -48190,11 +48190,11 @@
       </c>
       <c r="G78" s="15" t="n">
         <f aca="false">F78/px-1</f>
-        <v>0.00861588413064296</v>
+        <v>0.00861588413064407</v>
       </c>
       <c r="H78" s="16" t="n">
         <f aca="false">px/E78</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48217,15 +48217,15 @@
       </c>
       <c r="F79" s="19" t="n">
         <f aca="false">C79*E79</f>
-        <v>265.009734572012</v>
+        <v>265.009734572013</v>
       </c>
       <c r="G79" s="15" t="n">
         <f aca="false">F79/px-1</f>
-        <v>0.0816723860082138</v>
+        <v>0.0816723860082151</v>
       </c>
       <c r="H79" s="16" t="n">
         <f aca="false">px/E79</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48248,15 +48248,15 @@
       </c>
       <c r="F80" s="19" t="n">
         <f aca="false">C80*E80</f>
-        <v>307.753240148143</v>
+        <v>307.753240148144</v>
       </c>
       <c r="G80" s="15" t="n">
         <f aca="false">F80/px-1</f>
-        <v>0.256135674074055</v>
+        <v>0.256135674074056</v>
       </c>
       <c r="H80" s="16" t="n">
         <f aca="false">px/E80</f>
-        <v>9.17098386564957</v>
+        <v>9.17098386564956</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48334,7 +48334,7 @@
       </c>
       <c r="B91" s="16" t="n">
         <f aca="false">PL!G200</f>
-        <v>33.6604474903365</v>
+        <v>33.6604474903366</v>
       </c>
       <c r="C91" s="16" t="n">
         <f aca="false">PL!G212</f>
@@ -48351,7 +48351,7 @@
       </c>
       <c r="B92" s="16" t="n">
         <f aca="false">PL!H200</f>
-        <v>34.8921060489596</v>
+        <v>34.8921060489597</v>
       </c>
       <c r="C92" s="16" t="n">
         <f aca="false">PL!H212</f>
@@ -48436,11 +48436,11 @@
       </c>
       <c r="B98" s="16" t="n">
         <f aca="false">B90*(1-$B$96)</f>
-        <v>18.9501804070511</v>
+        <v>18.9501804070512</v>
       </c>
       <c r="C98" s="16" t="n">
         <f aca="false">C90*(1-$B$96)</f>
-        <v>16.7113731907031</v>
+        <v>16.7113731907032</v>
       </c>
       <c r="D98" s="16" t="n">
         <f aca="false">D90*(1-$B$96)</f>
@@ -48545,7 +48545,7 @@
       </c>
       <c r="C104" s="28" t="n">
         <f aca="false">C103*(1+tp_r)</f>
-        <v>288.326387640667</v>
+        <v>288.326387640668</v>
       </c>
       <c r="D104" s="28" t="n">
         <f aca="false">D103*(1+tp_r)</f>
@@ -48558,7 +48558,7 @@
       </c>
       <c r="B105" s="31" t="n">
         <f aca="false">tp_wA*B104+tp_wB*C104+tp_wC*D104</f>
-        <v>290.30634608678</v>
+        <v>290.306346086781</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>615</v>
@@ -48707,7 +48707,7 @@
       </c>
       <c r="B115" s="16" t="n">
         <f aca="false">tp_wA*(0.166666666666667*B89+0.833333333333333*B90)+tp_wB*(0.166666666666667*C89+0.833333333333333*C90)+tp_wC*(0.166666666666667*D89+0.833333333333333*D90)</f>
-        <v>27.7834620113047</v>
+        <v>27.7834620113048</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>641</v>
@@ -48749,7 +48749,7 @@
       </c>
       <c r="B120" s="31" t="n">
         <f aca="false">tp_w_dcf*B105+(1-tp_w_dcf)*B116</f>
-        <v>349.917288066706</v>
+        <v>349.917288066707</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>647</v>
@@ -48785,7 +48785,7 @@
       </c>
       <c r="B123" s="15" t="n">
         <f aca="false">B120/px-1</f>
-        <v>0.428233828843698</v>
+        <v>0.4282338288437</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>652</v>
@@ -48797,7 +48797,7 @@
       </c>
       <c r="B124" s="15" t="n">
         <f aca="false">B121/px-1</f>
-        <v>0.671543796108702</v>
+        <v>0.671543796108704</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48806,7 +48806,7 @@
       </c>
       <c r="B125" s="15" t="n">
         <f aca="false">B115/cons_feps-1</f>
-        <v>0.31898940738428</v>
+        <v>0.318989407384281</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>655</v>
@@ -49133,7 +49133,7 @@
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">C7/B7-1</f>
-        <v>-0.0202970738974246</v>
+        <v>-0.0202970738974242</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">PL!E125</f>
@@ -49141,7 +49141,7 @@
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">E7/B7-1</f>
-        <v>-0.0202970738974246</v>
+        <v>-0.0202970738974242</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">PL!E169</f>
@@ -49149,7 +49149,7 @@
       </c>
       <c r="H7" s="15" t="n">
         <f aca="false">G7/B7-1</f>
-        <v>-0.0202970738974246</v>
+        <v>-0.0202970738974242</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>681</v>
@@ -49172,7 +49172,7 @@
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.179977517008918</v>
+        <v>0.179977517008919</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">PL!E144</f>
@@ -49180,7 +49180,7 @@
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>0.179977517008918</v>
+        <v>0.179977517008919</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">PL!E188</f>
@@ -49188,7 +49188,7 @@
       </c>
       <c r="H8" s="15" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>0.179977517008918</v>
+        <v>0.179977517008919</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>681</v>
@@ -49208,7 +49208,7 @@
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.214304135685541</v>
+        <v>0.214304135685542</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">PL!E144</f>
@@ -49216,7 +49216,7 @@
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>0.214304135685541</v>
+        <v>0.214304135685542</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">PL!E188</f>
@@ -49224,7 +49224,7 @@
       </c>
       <c r="H9" s="15" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>0.214304135685541</v>
+        <v>0.214304135685542</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>689</v>
@@ -49244,7 +49244,7 @@
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.0685876394032758</v>
+        <v>0.068587639403277</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">PL!E144</f>
@@ -49252,7 +49252,7 @@
       </c>
       <c r="F10" s="15" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.0685876394032758</v>
+        <v>0.068587639403277</v>
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">PL!E188</f>
@@ -49260,7 +49260,7 @@
       </c>
       <c r="H10" s="15" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>0.0685876394032758</v>
+        <v>0.068587639403277</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>691</v>
@@ -49283,7 +49283,7 @@
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.12205015568066</v>
+        <v>0.122050155680661</v>
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">PL!F144</f>
@@ -49291,7 +49291,7 @@
       </c>
       <c r="F11" s="15" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>-0.0105107979188933</v>
+        <v>-0.0105107979188922</v>
       </c>
       <c r="G11" s="22" t="n">
         <f aca="false">PL!F188</f>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">C12-B12</f>
-        <v>0.00458164102023861</v>
+        <v>0.00458164102023862</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">PL!E135</f>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="F12" s="15" t="n">
         <f aca="false">E12-B12</f>
-        <v>0.00458164102023861</v>
+        <v>0.00458164102023862</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">PL!E179</f>
@@ -49338,7 +49338,7 @@
       </c>
       <c r="H12" s="15" t="n">
         <f aca="false">G12-B12</f>
-        <v>0.00458164102023861</v>
+        <v>0.00458164102023862</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>681</v>
@@ -49476,15 +49476,15 @@
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">Units!C10/(Units!C14*Units!C6)</f>
-        <v>1.30407103943906</v>
+        <v>1.30407103943907</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">Units!C10/(Units!C14*Units!C6)</f>
-        <v>1.30407103943906</v>
+        <v>1.30407103943907</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">Units!C10/(Units!C14*Units!C6)</f>
-        <v>1.30407103943906</v>
+        <v>1.30407103943907</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>705</v>
@@ -49535,7 +49535,7 @@
       </c>
       <c r="D21" s="15" t="n">
         <f aca="false">C21-B21</f>
-        <v>0.000972715169162426</v>
+        <v>0.000972715169162433</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">PL!E135</f>
@@ -49543,7 +49543,7 @@
       </c>
       <c r="F21" s="15" t="n">
         <f aca="false">E21-B21</f>
-        <v>0.000972715169162426</v>
+        <v>0.000972715169162433</v>
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">PL!E179</f>
@@ -49551,7 +49551,7 @@
       </c>
       <c r="H21" s="15" t="n">
         <f aca="false">G21-B21</f>
-        <v>0.000972715169162426</v>
+        <v>0.000972715169162433</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>712</v>
@@ -49628,11 +49628,11 @@
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">Val!B115</f>
-        <v>27.7834620113047</v>
+        <v>27.7834620113048</v>
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">C28/B28-1</f>
-        <v>0.31898940738428</v>
+        <v>0.318989407384281</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>343</v>
@@ -49651,11 +49651,11 @@
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">Val!B120</f>
-        <v>349.917288066706</v>
+        <v>349.917288066707</v>
       </c>
       <c r="D29" s="15" t="n">
         <f aca="false">C29/B29-1</f>
-        <v>0.00710113128998735</v>
+        <v>0.00710113128998846</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>339</v>
@@ -49678,7 +49678,7 @@
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">C30/B30-1</f>
-        <v>0.178668096263152</v>
+        <v>0.178668096263153</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>38</v>
@@ -49767,7 +49767,7 @@
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">PL!E74</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E4" s="14" t="n">
         <f aca="false">PL!E91</f>
@@ -49787,7 +49787,7 @@
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">PL!F74</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J4" s="14" t="n">
         <f aca="false">PL!F91</f>
@@ -49827,7 +49827,7 @@
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">F5/F$4-1</f>
-        <v>-0.0781102060017744</v>
+        <v>-0.0781102060017745</v>
       </c>
       <c r="H5" s="19" t="n">
         <f aca="false">F61</f>
@@ -49835,7 +49835,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">F54</f>
-        <v>4840.75325255667</v>
+        <v>4840.75325255668</v>
       </c>
       <c r="J5" s="14" t="n">
         <f aca="false">F71</f>
@@ -49843,7 +49843,7 @@
       </c>
       <c r="K5" s="16" t="n">
         <f aca="false">F80</f>
-        <v>26.933780602971</v>
+        <v>26.9337806029711</v>
       </c>
       <c r="L5" s="15" t="n">
         <f aca="false">K5/K$4-1</f>
@@ -49863,11 +49863,11 @@
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">E98</f>
-        <v>6587.40058588118</v>
+        <v>6587.40058588119</v>
       </c>
       <c r="E6" s="14" t="n">
         <f aca="false">E115</f>
-        <v>0.0615308423384565</v>
+        <v>0.0615308423384564</v>
       </c>
       <c r="F6" s="16" t="n">
         <f aca="false">E124</f>
@@ -49875,7 +49875,7 @@
       </c>
       <c r="G6" s="15" t="n">
         <f aca="false">F6/F$4-1</f>
-        <v>0.0781102060017751</v>
+        <v>0.0781102060017747</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">F105</f>
@@ -49883,7 +49883,7 @@
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">F98</f>
-        <v>7422.4883205869</v>
+        <v>7422.48832058691</v>
       </c>
       <c r="J6" s="14" t="n">
         <f aca="false">F115</f>
@@ -49911,7 +49911,7 @@
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">E142</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">E159</f>
@@ -49923,7 +49923,7 @@
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">F7/F$4-1</f>
-        <v>-0.00406247260718007</v>
+        <v>-0.0040624726071804</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">F149</f>
@@ -49931,7 +49931,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">F142</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="J7" s="14" t="n">
         <f aca="false">F159</f>
@@ -49943,7 +49943,7 @@
       </c>
       <c r="L7" s="15" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.00664943248346428</v>
+        <v>-0.0066494324834645</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49959,7 +49959,7 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">E186</f>
-        <v>4773.47868542114</v>
+        <v>4773.47868542115</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">E203</f>
@@ -49971,7 +49971,7 @@
       </c>
       <c r="G8" s="15" t="n">
         <f aca="false">F8/F$4-1</f>
-        <v>0.00609370891077088</v>
+        <v>0.00609370891077043</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">F193</f>
@@ -49979,7 +49979,7 @@
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">F186</f>
-        <v>4840.75325255667</v>
+        <v>4840.75325255668</v>
       </c>
       <c r="J8" s="14" t="n">
         <f aca="false">F203</f>
@@ -49991,7 +49991,7 @@
       </c>
       <c r="L8" s="15" t="n">
         <f aca="false">K8/K$4-1</f>
-        <v>0.00754715780794091</v>
+        <v>0.00754715780794113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50007,7 +50007,7 @@
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">E230</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E9" s="14" t="n">
         <f aca="false">E247</f>
@@ -50019,7 +50019,7 @@
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.0123843768920692</v>
+        <v>-0.0123843768920695</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">F237</f>
@@ -50027,7 +50027,7 @@
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">F230</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J9" s="14" t="n">
         <f aca="false">F247</f>
@@ -50039,7 +50039,7 @@
       </c>
       <c r="L9" s="15" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>-0.0266975851646587</v>
+        <v>-0.0266975851646588</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50055,11 +50055,11 @@
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">E274</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E10" s="14" t="n">
         <f aca="false">E291</f>
-        <v>0.0618374292095398</v>
+        <v>0.0618374292095399</v>
       </c>
       <c r="F10" s="16" t="n">
         <f aca="false">E300</f>
@@ -50067,7 +50067,7 @@
       </c>
       <c r="G10" s="15" t="n">
         <f aca="false">F10/F$4-1</f>
-        <v>0.00619218844603475</v>
+        <v>0.00619218844603453</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">F281</f>
@@ -50075,7 +50075,7 @@
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">F274</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J10" s="14" t="n">
         <f aca="false">F291</f>
@@ -50087,7 +50087,7 @@
       </c>
       <c r="L10" s="15" t="n">
         <f aca="false">K10/K$4-1</f>
-        <v>0.0133487925823297</v>
+        <v>0.0133487925823295</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50103,7 +50103,7 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">E318</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">E335</f>
@@ -50123,7 +50123,7 @@
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">F318</f>
-        <v>5486.18701956423</v>
+        <v>5486.18701956424</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">F335</f>
@@ -50151,7 +50151,7 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">E362</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">E379</f>
@@ -50171,7 +50171,7 @@
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">F362</f>
-        <v>7745.20520409068</v>
+        <v>7745.20520409069</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">F379</f>
@@ -50207,11 +50207,11 @@
       </c>
       <c r="F13" s="16" t="n">
         <f aca="false">E432</f>
-        <v>23.9324376302572</v>
+        <v>23.9324376302573</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">F13/F$4-1</f>
-        <v>-0.104146941335699</v>
+        <v>-0.1041469413357</v>
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">F413</f>
@@ -50219,7 +50219,7 @@
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">F406</f>
-        <v>5163.47013606045</v>
+        <v>5163.47013606046</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">F423</f>
@@ -50243,11 +50243,11 @@
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">E457</f>
-        <v>14880.4830664064</v>
+        <v>14880.4830664065</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">E450</f>
-        <v>6873.80930700645</v>
+        <v>6873.80930700646</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">E467</f>
@@ -50267,7 +50267,7 @@
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">F450</f>
-        <v>7745.20520409068</v>
+        <v>7745.20520409069</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">F467</f>
@@ -50295,7 +50295,7 @@
       </c>
       <c r="D15" s="19" t="n">
         <f aca="false">E494</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E15" s="14" t="n">
         <f aca="false">E511</f>
@@ -50307,7 +50307,7 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">F15/F$4-1</f>
-        <v>-0.0344116180680679</v>
+        <v>-0.0344116180680685</v>
       </c>
       <c r="H15" s="19" t="n">
         <f aca="false">F501</f>
@@ -50315,7 +50315,7 @@
       </c>
       <c r="I15" s="19" t="n">
         <f aca="false">F494</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J15" s="14" t="n">
         <f aca="false">F511</f>
@@ -50327,7 +50327,7 @@
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.054939605534176</v>
+        <v>-0.0549396055341763</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50343,7 +50343,7 @@
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">E538</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E16" s="14" t="n">
         <f aca="false">E555</f>
@@ -50355,7 +50355,7 @@
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">F16/F$4-1</f>
-        <v>0.0156416445763952</v>
+        <v>0.0156416445763949</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">F545</f>
@@ -50363,7 +50363,7 @@
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">F538</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J16" s="14" t="n">
         <f aca="false">F555</f>
@@ -50391,7 +50391,7 @@
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">E582</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E17" s="14" t="n">
         <f aca="false">E599</f>
@@ -50403,7 +50403,7 @@
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0265282292015652</v>
+        <v>-0.0265282292015653</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">F589</f>
@@ -50411,7 +50411,7 @@
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">F582</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J17" s="14" t="n">
         <f aca="false">F599</f>
@@ -50423,7 +50423,7 @@
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.0494097969472233</v>
+        <v>-0.0494097969472235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">E626</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">E643</f>
@@ -50451,7 +50451,7 @@
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">F18/F$4-1</f>
-        <v>0.0287389149683628</v>
+        <v>0.0287389149683626</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">F633</f>
@@ -50459,7 +50459,7 @@
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">F626</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J18" s="14" t="n">
         <f aca="false">F643</f>
@@ -50471,7 +50471,7 @@
       </c>
       <c r="L18" s="15" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>0.0553829271056525</v>
+        <v>0.0553829271056523</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50487,7 +50487,7 @@
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">E670</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">E687</f>
@@ -50499,7 +50499,7 @@
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">F19/F$4-1</f>
-        <v>-0.0308648522937639</v>
+        <v>-0.0308648522937642</v>
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">F677</f>
@@ -50507,7 +50507,7 @@
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">F670</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J19" s="14" t="n">
         <f aca="false">F687</f>
@@ -50515,11 +50515,11 @@
       </c>
       <c r="K19" s="16" t="n">
         <f aca="false">F696</f>
-        <v>30.1247127690198</v>
+        <v>30.1247127690199</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">K19/K$4-1</f>
-        <v>-0.0411457157715808</v>
+        <v>-0.041145715771581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50535,7 +50535,7 @@
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">E714</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E20" s="14" t="n">
         <f aca="false">E731</f>
@@ -50547,7 +50547,7 @@
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">F20/F$4-1</f>
-        <v>0.030864852293764</v>
+        <v>0.0308648522937638</v>
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">F721</f>
@@ -50555,7 +50555,7 @@
       </c>
       <c r="I20" s="19" t="n">
         <f aca="false">F714</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J20" s="14" t="n">
         <f aca="false">F731</f>
@@ -50567,7 +50567,7 @@
       </c>
       <c r="L20" s="15" t="n">
         <f aca="false">K20/K$4-1</f>
-        <v>0.0411457157715804</v>
+        <v>0.0411457157715807</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50583,7 +50583,7 @@
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">E758</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">E775</f>
@@ -50595,7 +50595,7 @@
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">F21/F$4-1</f>
-        <v>-0.0333173144244516</v>
+        <v>-0.0333173144244521</v>
       </c>
       <c r="H21" s="19" t="n">
         <f aca="false">F765</f>
@@ -50603,7 +50603,7 @@
       </c>
       <c r="I21" s="19" t="n">
         <f aca="false">F758</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J21" s="14" t="n">
         <f aca="false">F775</f>
@@ -50615,7 +50615,7 @@
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">K21/K$4-1</f>
-        <v>-0.0355491067869062</v>
+        <v>-0.0355491067869059</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50631,7 +50631,7 @@
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">E802</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">E819</f>
@@ -50651,7 +50651,7 @@
       </c>
       <c r="I22" s="19" t="n">
         <f aca="false">F802</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J22" s="14" t="n">
         <f aca="false">F819</f>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="L22" s="15" t="n">
         <f aca="false">K22/K$4-1</f>
-        <v>0.023699404524604</v>
+        <v>0.0236994045246044</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50679,7 +50679,7 @@
       </c>
       <c r="D23" s="19" t="n">
         <f aca="false">E846</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">E863</f>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="G23" s="15" t="n">
         <f aca="false">F23/F$4-1</f>
-        <v>-0.0484165313727029</v>
+        <v>-0.0484165313727031</v>
       </c>
       <c r="H23" s="19" t="n">
         <f aca="false">F853</f>
@@ -50699,7 +50699,7 @@
       </c>
       <c r="I23" s="19" t="n">
         <f aca="false">F846</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J23" s="14" t="n">
         <f aca="false">F863</f>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">K23/K$4-1</f>
-        <v>-0.0442956688098249</v>
+        <v>-0.0442956688098248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50727,7 +50727,7 @@
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">E890</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">E907</f>
@@ -50747,7 +50747,7 @@
       </c>
       <c r="I24" s="19" t="n">
         <f aca="false">F890</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J24" s="14" t="n">
         <f aca="false">F907</f>
@@ -50775,7 +50775,7 @@
       </c>
       <c r="D25" s="19" t="n">
         <f aca="false">E934</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">E951</f>
@@ -50795,7 +50795,7 @@
       </c>
       <c r="I25" s="19" t="n">
         <f aca="false">F934</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">F951</f>
@@ -50803,7 +50803,7 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">F960</f>
-        <v>34.7495533062313</v>
+        <v>34.7495533062314</v>
       </c>
       <c r="L25" s="15" t="n">
         <f aca="false">K25/K$4-1</f>
@@ -50823,7 +50823,7 @@
       </c>
       <c r="D26" s="19" t="n">
         <f aca="false">PL!E118</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">PL!E135</f>
@@ -50843,7 +50843,7 @@
       </c>
       <c r="I26" s="19" t="n">
         <f aca="false">PL!F118</f>
-        <v>5163.47013606045</v>
+        <v>5163.47013606046</v>
       </c>
       <c r="J26" s="14" t="n">
         <f aca="false">PL!F135</f>
@@ -50855,7 +50855,7 @@
       </c>
       <c r="L26" s="15" t="n">
         <f aca="false">K26/K$4-1</f>
-        <v>-0.118141736292652</v>
+        <v>-0.118141736292651</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50871,7 +50871,7 @@
       </c>
       <c r="D27" s="19" t="n">
         <f aca="false">PL!E162</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">PL!E179</f>
@@ -50903,7 +50903,7 @@
       </c>
       <c r="L27" s="15" t="n">
         <f aca="false">K27/K$4-1</f>
-        <v>-0.248959903599479</v>
+        <v>-0.24895990359948</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50956,7 +50956,7 @@
       </c>
       <c r="D43" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51055,7 +51055,7 @@
       </c>
       <c r="D47" s="19" t="n">
         <f aca="false">D45*D46</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E47" s="19" t="n">
         <f aca="false">E45*E46</f>
@@ -51079,7 +51079,7 @@
       </c>
       <c r="D48" s="19" t="n">
         <f aca="false">D47*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E48" s="19" t="n">
         <f aca="false">E47*fx</f>
@@ -51150,11 +51150,11 @@
       </c>
       <c r="F51" s="15" t="n">
         <f aca="false">$D$49*F50</f>
-        <v>0.130957543177441</v>
+        <v>0.130957543177442</v>
       </c>
       <c r="G51" s="15" t="n">
         <f aca="false">$D$49*G50</f>
-        <v>0.122227040298945</v>
+        <v>0.122227040298946</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51170,15 +51170,15 @@
       </c>
       <c r="E52" s="19" t="n">
         <f aca="false">E48*E51</f>
-        <v>5409.94251014396</v>
+        <v>5409.94251014397</v>
       </c>
       <c r="F52" s="19" t="n">
         <f aca="false">F48*F51</f>
-        <v>6050.94156569584</v>
+        <v>6050.94156569585</v>
       </c>
       <c r="G52" s="19" t="n">
         <f aca="false">G48*G51</f>
-        <v>6433.44714659664</v>
+        <v>6433.44714659665</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51229,11 +51229,11 @@
       </c>
       <c r="F54" s="19" t="n">
         <f aca="false">F52*(1-F53)</f>
-        <v>4840.75325255667</v>
+        <v>4840.75325255668</v>
       </c>
       <c r="G54" s="19" t="n">
         <f aca="false">G52*(1-G53)</f>
-        <v>4825.08535994748</v>
+        <v>4825.08535994749</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51422,7 +51422,7 @@
       </c>
       <c r="E62" s="15" t="n">
         <f aca="false">E61/D61-1</f>
-        <v>0.154688190377546</v>
+        <v>0.154688190377547</v>
       </c>
       <c r="F62" s="15" t="n">
         <f aca="false">F61/E61-1</f>
@@ -51430,7 +51430,7 @@
       </c>
       <c r="G62" s="15" t="n">
         <f aca="false">G61/F61-1</f>
-        <v>0.0196062217701023</v>
+        <v>0.0196062217701025</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51502,11 +51502,11 @@
       </c>
       <c r="E65" s="16" t="n">
         <f aca="false">E54/fx/E45</f>
-        <v>3.65345615871512</v>
+        <v>3.65345615871513</v>
       </c>
       <c r="F65" s="16" t="n">
         <f aca="false">F54/fx/F45</f>
-        <v>2.86545581075696</v>
+        <v>2.86545581075697</v>
       </c>
       <c r="G65" s="16" t="n">
         <f aca="false">G54/fx/G45</f>
@@ -51573,7 +51573,7 @@
       </c>
       <c r="E69" s="22" t="n">
         <f aca="false">($D$68+d_ai+vrd)*E52*(1-E53*(1-keep))</f>
-        <v>295.636785321261</v>
+        <v>295.636785321262</v>
       </c>
       <c r="F69" s="22" t="n">
         <f aca="false">($D$68+d_ai+vrd)*F52*(1-F53*(1-keep))</f>
@@ -51581,7 +51581,7 @@
       </c>
       <c r="G69" s="22" t="n">
         <f aca="false">($D$68+d_ai+vrd)*G52*(1-G53*(1-keep))</f>
-        <v>346.24138771151</v>
+        <v>346.241387711511</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>472</v>
@@ -51604,15 +51604,15 @@
       </c>
       <c r="E70" s="19" t="n">
         <f aca="false">$D$68*E60+E69</f>
-        <v>793.643292795939</v>
+        <v>793.64329279594</v>
       </c>
       <c r="F70" s="19" t="n">
         <f aca="false">$D$68*F60+F69</f>
-        <v>845.039625161656</v>
+        <v>845.039625161657</v>
       </c>
       <c r="G70" s="19" t="n">
         <f aca="false">$D$68*G60+G69</f>
-        <v>880.983824740027</v>
+        <v>880.983824740028</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51640,7 +51640,7 @@
       </c>
       <c r="G71" s="14" t="n">
         <f aca="false">G70/G61</f>
-        <v>0.0656354448746166</v>
+        <v>0.0656354448746167</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51751,7 +51751,7 @@
       </c>
       <c r="G75" s="19" t="n">
         <f aca="false">G70-G74</f>
-        <v>605.81791662453</v>
+        <v>605.817916624531</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51831,7 +51831,7 @@
       </c>
       <c r="F78" s="19" t="n">
         <f aca="false">F75*F77</f>
-        <v>377.529840791109</v>
+        <v>377.52984079111</v>
       </c>
       <c r="G78" s="19" t="n">
         <f aca="false">G75*G77</f>
@@ -51887,11 +51887,11 @@
       </c>
       <c r="F80" s="22" t="n">
         <f aca="false">F78/F79</f>
-        <v>26.933780602971</v>
+        <v>26.9337806029711</v>
       </c>
       <c r="G80" s="22" t="n">
         <f aca="false">G78/G79</f>
-        <v>28.5254222542106</v>
+        <v>28.5254222542107</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51907,15 +51907,15 @@
       </c>
       <c r="E81" s="15" t="n">
         <f aca="false">E80/D80-1</f>
-        <v>0.254135954623211</v>
+        <v>0.254135954623212</v>
       </c>
       <c r="F81" s="15" t="n">
         <f aca="false">F80/E80-1</f>
-        <v>0.0936243114864834</v>
+        <v>0.0936243114864832</v>
       </c>
       <c r="G81" s="15" t="n">
         <f aca="false">G80/F80-1</f>
-        <v>0.0590946245052579</v>
+        <v>0.0590946245052584</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51963,7 +51963,7 @@
       </c>
       <c r="D87" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E87" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -52062,7 +52062,7 @@
       </c>
       <c r="D91" s="19" t="n">
         <f aca="false">D89*D90</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E91" s="19" t="n">
         <f aca="false">E89*E90</f>
@@ -52086,7 +52086,7 @@
       </c>
       <c r="D92" s="19" t="n">
         <f aca="false">D91*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E92" s="19" t="n">
         <f aca="false">E91*fx</f>
@@ -52177,11 +52177,11 @@
       </c>
       <c r="E96" s="19" t="n">
         <f aca="false">E92*E95</f>
-        <v>7319.33398431242</v>
+        <v>7319.33398431243</v>
       </c>
       <c r="F96" s="19" t="n">
         <f aca="false">F92*F95</f>
-        <v>9278.11040073362</v>
+        <v>9278.11040073363</v>
       </c>
       <c r="G96" s="19" t="n">
         <f aca="false">G92*G95</f>
@@ -52232,15 +52232,15 @@
       </c>
       <c r="E98" s="19" t="n">
         <f aca="false">E96*(1-E97)</f>
-        <v>6587.40058588118</v>
+        <v>6587.40058588119</v>
       </c>
       <c r="F98" s="19" t="n">
         <f aca="false">F96*(1-F97)</f>
-        <v>7422.4883205869</v>
+        <v>7422.48832058691</v>
       </c>
       <c r="G98" s="19" t="n">
         <f aca="false">G96*(1-G97)</f>
-        <v>7926.92594848514</v>
+        <v>7926.92594848515</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52429,7 +52429,7 @@
       </c>
       <c r="E106" s="15" t="n">
         <f aca="false">E105/D105-1</f>
-        <v>0.30879931639315</v>
+        <v>0.308799316393151</v>
       </c>
       <c r="F106" s="15" t="n">
         <f aca="false">F105/E105-1</f>
@@ -52437,7 +52437,7 @@
       </c>
       <c r="G106" s="15" t="n">
         <f aca="false">G105/F105-1</f>
-        <v>0.0494224975953086</v>
+        <v>0.0494224975953088</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52457,15 +52457,15 @@
       </c>
       <c r="E107" s="15" t="n">
         <f aca="false">E98/E105</f>
-        <v>0.451375019068005</v>
+        <v>0.451375019068006</v>
       </c>
       <c r="F107" s="15" t="n">
         <f aca="false">F98/F105</f>
-        <v>0.471388444943655</v>
+        <v>0.471388444943656</v>
       </c>
       <c r="G107" s="15" t="n">
         <f aca="false">G98/G105</f>
-        <v>0.479715598610191</v>
+        <v>0.479715598610192</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="F108" s="15" t="n">
         <f aca="false">(F98+F100)/F105</f>
-        <v>0.652986228498763</v>
+        <v>0.652986228498764</v>
       </c>
       <c r="G108" s="15" t="n">
         <f aca="false">(G98+G100)/G105</f>
@@ -52513,11 +52513,11 @@
       </c>
       <c r="F109" s="16" t="n">
         <f aca="false">F98/fx/F89</f>
-        <v>4.39369890982734</v>
+        <v>4.39369890982735</v>
       </c>
       <c r="G109" s="16" t="n">
         <f aca="false">G98/fx/G89</f>
-        <v>4.11909272796313</v>
+        <v>4.11909272796314</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52537,11 +52537,11 @@
       </c>
       <c r="F110" s="19" t="n">
         <f aca="false">F96/fx/odm_vr</f>
-        <v>42.9542148182112</v>
+        <v>42.9542148182113</v>
       </c>
       <c r="G110" s="19" t="n">
         <f aca="false">G96/fx/odm_vr</f>
-        <v>48.9316416573157</v>
+        <v>48.9316416573158</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>467</v>
@@ -52580,15 +52580,15 @@
       </c>
       <c r="E113" s="22" t="n">
         <f aca="false">($D$112+d_ai+vrd)*E96*(1-E97*(1-keep))</f>
-        <v>399.97918014053</v>
+        <v>399.979180140531</v>
       </c>
       <c r="F113" s="22" t="n">
         <f aca="false">($D$112+d_ai+vrd)*F96*(1-F97*(1-keep))</f>
-        <v>501.89889348723</v>
+        <v>501.898893487231</v>
       </c>
       <c r="G113" s="22" t="n">
         <f aca="false">($D$112+d_ai+vrd)*G96*(1-G97*(1-keep))</f>
-        <v>568.825136954624</v>
+        <v>568.825136954625</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>472</v>
@@ -52611,7 +52611,7 @@
       </c>
       <c r="E114" s="19" t="n">
         <f aca="false">$D$112*E104+E113</f>
-        <v>897.985687615208</v>
+        <v>897.985687615209</v>
       </c>
       <c r="F114" s="19" t="n">
         <f aca="false">$D$112*F104+F113</f>
@@ -52639,7 +52639,7 @@
       </c>
       <c r="E115" s="14" t="n">
         <f aca="false">E114/E105</f>
-        <v>0.0615308423384565</v>
+        <v>0.0615308423384564</v>
       </c>
       <c r="F115" s="14" t="n">
         <f aca="false">F114/F105</f>
@@ -52698,11 +52698,11 @@
       </c>
       <c r="F117" s="19" t="n">
         <f aca="false">E117*(1+MAX(0,phi*F106))</f>
-        <v>295.34651059056</v>
+        <v>295.346510590561</v>
       </c>
       <c r="G117" s="19" t="n">
         <f aca="false">F117*(1+MAX(0,phi*G106))</f>
-        <v>301.185215474338</v>
+        <v>301.185215474339</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52726,11 +52726,11 @@
       </c>
       <c r="F118" s="19" t="n">
         <f aca="false">F117+0*F105</f>
-        <v>295.34651059056</v>
+        <v>295.346510590561</v>
       </c>
       <c r="G118" s="19" t="n">
         <f aca="false">G117+0*G105</f>
-        <v>301.185215474338</v>
+        <v>301.185215474339</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52750,15 +52750,15 @@
       </c>
       <c r="E119" s="19" t="n">
         <f aca="false">E114-E118</f>
-        <v>611.678680110721</v>
+        <v>611.678680110722</v>
       </c>
       <c r="F119" s="19" t="n">
         <f aca="false">F114-F118</f>
-        <v>724.266642740567</v>
+        <v>724.266642740568</v>
       </c>
       <c r="G119" s="19" t="n">
         <f aca="false">G114-G118</f>
-        <v>802.382358508803</v>
+        <v>802.382358508804</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52786,7 +52786,7 @@
       </c>
       <c r="G120" s="14" t="n">
         <f aca="false">G119/G105</f>
-        <v>0.0485579575143964</v>
+        <v>0.0485579575143963</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52838,7 +52838,7 @@
       </c>
       <c r="F122" s="19" t="n">
         <f aca="false">F119*F121</f>
-        <v>478.015984208774</v>
+        <v>478.015984208775</v>
       </c>
       <c r="G122" s="19" t="n">
         <f aca="false">G119*G121</f>
@@ -52898,7 +52898,7 @@
       </c>
       <c r="G124" s="22" t="n">
         <f aca="false">G122/G123</f>
-        <v>37.7808165749224</v>
+        <v>37.7808165749225</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52914,7 +52914,7 @@
       </c>
       <c r="E125" s="15" t="n">
         <f aca="false">E124/D124-1</f>
-        <v>0.466657708107424</v>
+        <v>0.466657708107425</v>
       </c>
       <c r="F125" s="15" t="n">
         <f aca="false">F124/E124-1</f>
@@ -52970,7 +52970,7 @@
       </c>
       <c r="D131" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E131" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -53069,7 +53069,7 @@
       </c>
       <c r="D135" s="19" t="n">
         <f aca="false">D133*D134</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E135" s="19" t="n">
         <f aca="false">E133*E134</f>
@@ -53093,7 +53093,7 @@
       </c>
       <c r="D136" s="19" t="n">
         <f aca="false">D135*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E136" s="19" t="n">
         <f aca="false">E135*fx</f>
@@ -53184,15 +53184,15 @@
       </c>
       <c r="E140" s="19" t="n">
         <f aca="false">E136*E139</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F140" s="19" t="n">
         <f aca="false">F136*F139</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G140" s="19" t="n">
         <f aca="false">G136*G139</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53239,15 +53239,15 @@
       </c>
       <c r="E142" s="19" t="n">
         <f aca="false">E140*(1-E141)</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F142" s="19" t="n">
         <f aca="false">F140*(1-F141)</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G142" s="19" t="n">
         <f aca="false">G140*(1-G141)</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53420,7 +53420,7 @@
       </c>
       <c r="G149" s="19" t="n">
         <f aca="false">G142+G148</f>
-        <v>17328.40060069</v>
+        <v>17328.4006006901</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53436,7 +53436,7 @@
       </c>
       <c r="E150" s="15" t="n">
         <f aca="false">E149/D149-1</f>
-        <v>0.288821948205942</v>
+        <v>0.288821948205943</v>
       </c>
       <c r="F150" s="15" t="n">
         <f aca="false">F149/E149-1</f>
@@ -53444,7 +53444,7 @@
       </c>
       <c r="G150" s="15" t="n">
         <f aca="false">G149/F149-1</f>
-        <v>0.0571611788487667</v>
+        <v>0.0571611788487669</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53468,7 +53468,7 @@
       </c>
       <c r="F151" s="15" t="n">
         <f aca="false">F142/F149</f>
-        <v>0.492203188368216</v>
+        <v>0.492203188368217</v>
       </c>
       <c r="G151" s="15" t="n">
         <f aca="false">G142/G149</f>
@@ -53492,11 +53492,11 @@
       </c>
       <c r="E152" s="15" t="n">
         <f aca="false">(E142+E144)/E149</f>
-        <v>0.627101322514718</v>
+        <v>0.627101322514719</v>
       </c>
       <c r="F152" s="15" t="n">
         <f aca="false">(F142+F144)/F149</f>
-        <v>0.66665033127801</v>
+        <v>0.666650331278011</v>
       </c>
       <c r="G152" s="15" t="n">
         <f aca="false">(G142+G144)/G149</f>
@@ -53516,15 +53516,15 @@
       </c>
       <c r="E153" s="16" t="n">
         <f aca="false">E142/fx/E133</f>
-        <v>4.77575968459493</v>
+        <v>4.77575968459494</v>
       </c>
       <c r="F153" s="16" t="n">
         <f aca="false">F142/fx/F133</f>
-        <v>4.77575968459493</v>
+        <v>4.77575968459494</v>
       </c>
       <c r="G153" s="16" t="n">
         <f aca="false">G142/fx/G133</f>
-        <v>4.53697170036519</v>
+        <v>4.5369717003652</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53540,11 +53540,11 @@
       </c>
       <c r="E154" s="19" t="n">
         <f aca="false">E140/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F154" s="19" t="n">
         <f aca="false">F140/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G154" s="19" t="n">
         <f aca="false">G140/fx/odm_vr</f>
@@ -53587,15 +53587,15 @@
       </c>
       <c r="E157" s="22" t="n">
         <f aca="false">($D$156+d_ai+vrd)*E140*(1-E141*(1-keep))</f>
-        <v>351.321194677672</v>
+        <v>351.321194677673</v>
       </c>
       <c r="F157" s="22" t="n">
         <f aca="false">($D$156+d_ai+vrd)*F140*(1-F141*(1-keep))</f>
-        <v>445.340633085386</v>
+        <v>445.340633085387</v>
       </c>
       <c r="G157" s="22" t="n">
         <f aca="false">($D$156+d_ai+vrd)*G140*(1-G141*(1-keep))</f>
-        <v>481.947719158879</v>
+        <v>481.94771915888</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>472</v>
@@ -53618,7 +53618,7 @@
       </c>
       <c r="E158" s="19" t="n">
         <f aca="false">$D$156*E148+E157</f>
-        <v>849.32770215235</v>
+        <v>849.327702152351</v>
       </c>
       <c r="F158" s="19" t="n">
         <f aca="false">$D$156*F148+F157</f>
@@ -53761,7 +53761,7 @@
       </c>
       <c r="F163" s="19" t="n">
         <f aca="false">F158-F162</f>
-        <v>662.800575984896</v>
+        <v>662.800575984897</v>
       </c>
       <c r="G163" s="19" t="n">
         <f aca="false">G158-G162</f>
@@ -53841,7 +53841,7 @@
       </c>
       <c r="E166" s="19" t="n">
         <f aca="false">E163*E165</f>
-        <v>372.937640542163</v>
+        <v>372.937640542164</v>
       </c>
       <c r="F166" s="19" t="n">
         <f aca="false">F163*F165</f>
@@ -53921,7 +53921,7 @@
       </c>
       <c r="E169" s="15" t="n">
         <f aca="false">E168/D168-1</f>
-        <v>0.354870256503001</v>
+        <v>0.354870256503002</v>
       </c>
       <c r="F169" s="15" t="n">
         <f aca="false">F168/E168-1</f>
@@ -53929,7 +53929,7 @@
       </c>
       <c r="G169" s="15" t="n">
         <f aca="false">G168/F168-1</f>
-        <v>0.070564372857137</v>
+        <v>0.0705643728571375</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="D175" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E175" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -54076,7 +54076,7 @@
       </c>
       <c r="D179" s="19" t="n">
         <f aca="false">D177*D178</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E179" s="19" t="n">
         <f aca="false">E177*E178</f>
@@ -54100,7 +54100,7 @@
       </c>
       <c r="D180" s="19" t="n">
         <f aca="false">D179*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E180" s="19" t="n">
         <f aca="false">E179*fx</f>
@@ -54191,15 +54191,15 @@
       </c>
       <c r="E184" s="19" t="n">
         <f aca="false">E180*E183</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F184" s="19" t="n">
         <f aca="false">F180*F183</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G184" s="19" t="n">
         <f aca="false">G180*G183</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54246,15 +54246,15 @@
       </c>
       <c r="E186" s="19" t="n">
         <f aca="false">E184*(1-E185)</f>
-        <v>4773.47868542114</v>
+        <v>4773.47868542115</v>
       </c>
       <c r="F186" s="19" t="n">
         <f aca="false">F184*(1-F185)</f>
-        <v>4840.75325255667</v>
+        <v>4840.75325255668</v>
       </c>
       <c r="G186" s="19" t="n">
         <f aca="false">G184*(1-G185)</f>
-        <v>4365.55342090486</v>
+        <v>4365.55342090487</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54443,7 +54443,7 @@
       </c>
       <c r="E194" s="15" t="n">
         <f aca="false">E193/D193-1</f>
-        <v>0.146126461154457</v>
+        <v>0.146126461154458</v>
       </c>
       <c r="F194" s="15" t="n">
         <f aca="false">F193/E193-1</f>
@@ -54471,7 +54471,7 @@
       </c>
       <c r="E195" s="15" t="n">
         <f aca="false">E186/E193</f>
-        <v>0.373507178887798</v>
+        <v>0.373507178887799</v>
       </c>
       <c r="F195" s="15" t="n">
         <f aca="false">F186/F193</f>
@@ -54499,7 +54499,7 @@
       </c>
       <c r="E196" s="15" t="n">
         <f aca="false">(E186+E188)/E193</f>
-        <v>0.580674544835212</v>
+        <v>0.580674544835213</v>
       </c>
       <c r="F196" s="15" t="n">
         <f aca="false">(F186+F188)/F193</f>
@@ -54523,15 +54523,15 @@
       </c>
       <c r="E197" s="16" t="n">
         <f aca="false">E186/fx/E177</f>
-        <v>3.5818197634462</v>
+        <v>3.58181976344621</v>
       </c>
       <c r="F197" s="16" t="n">
         <f aca="false">F186/fx/F177</f>
-        <v>2.86545581075696</v>
+        <v>2.86545581075697</v>
       </c>
       <c r="G197" s="16" t="n">
         <f aca="false">G186/fx/G177</f>
-        <v>2.26848585018259</v>
+        <v>2.2684858501826</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54547,11 +54547,11 @@
       </c>
       <c r="E198" s="19" t="n">
         <f aca="false">E184/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F198" s="19" t="n">
         <f aca="false">F184/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G198" s="19" t="n">
         <f aca="false">G184/fx/odm_vr</f>
@@ -54602,7 +54602,7 @@
       </c>
       <c r="G201" s="22" t="n">
         <f aca="false">($D$200+d_ai+vrd)*G184*(1-G185*(1-keep))</f>
-        <v>457.850333200935</v>
+        <v>457.850333200936</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>472</v>
@@ -54629,11 +54629,11 @@
       </c>
       <c r="F202" s="19" t="n">
         <f aca="false">$D$200*F192+F201</f>
-        <v>945.241267605868</v>
+        <v>945.241267605869</v>
       </c>
       <c r="G202" s="19" t="n">
         <f aca="false">$D$200*G192+G201</f>
-        <v>992.592770229452</v>
+        <v>992.592770229453</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54708,7 +54708,7 @@
       </c>
       <c r="E205" s="19" t="n">
         <f aca="false">D205*(1+MAX(0,phi*E194))</f>
-        <v>269.725410480528</v>
+        <v>269.725410480529</v>
       </c>
       <c r="F205" s="19" t="n">
         <f aca="false">E205*(1+MAX(0,phi*F194))</f>
@@ -54736,7 +54736,7 @@
       </c>
       <c r="E206" s="19" t="n">
         <f aca="false">E205+0*E193</f>
-        <v>269.725410480528</v>
+        <v>269.725410480529</v>
       </c>
       <c r="F206" s="19" t="n">
         <f aca="false">F205+0*F193</f>
@@ -54856,7 +54856,7 @@
       </c>
       <c r="G210" s="19" t="n">
         <f aca="false">G207*G209</f>
-        <v>474.952218540481</v>
+        <v>474.952218540482</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="E213" s="15" t="n">
         <f aca="false">E212/D212-1</f>
-        <v>0.368686693658792</v>
+        <v>0.368686693658793</v>
       </c>
       <c r="F213" s="15" t="n">
         <f aca="false">F212/E212-1</f>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="G213" s="15" t="n">
         <f aca="false">G212/F212-1</f>
-        <v>0.0704349239492825</v>
+        <v>0.0704349239492823</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54984,7 +54984,7 @@
       </c>
       <c r="D219" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E219" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55083,7 +55083,7 @@
       </c>
       <c r="D223" s="19" t="n">
         <f aca="false">D221*D222</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E223" s="19" t="n">
         <f aca="false">E221*E222</f>
@@ -55107,7 +55107,7 @@
       </c>
       <c r="D224" s="19" t="n">
         <f aca="false">D223*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E224" s="19" t="n">
         <f aca="false">E223*fx</f>
@@ -55198,15 +55198,15 @@
       </c>
       <c r="E228" s="19" t="n">
         <f aca="false">E224*E227</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F228" s="19" t="n">
         <f aca="false">F224*F227</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G228" s="19" t="n">
         <f aca="false">G224*G227</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55253,15 +55253,15 @@
       </c>
       <c r="E230" s="19" t="n">
         <f aca="false">E228*(1-E229)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F230" s="19" t="n">
         <f aca="false">F228*(1-F229)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G230" s="19" t="n">
         <f aca="false">G228*(1-G229)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55450,7 +55450,7 @@
       </c>
       <c r="E238" s="15" t="n">
         <f aca="false">E237/D237-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F238" s="15" t="n">
         <f aca="false">F237/E237-1</f>
@@ -55478,11 +55478,11 @@
       </c>
       <c r="E239" s="15" t="n">
         <f aca="false">E230/E237</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F239" s="15" t="n">
         <f aca="false">F230/F237</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G239" s="15" t="n">
         <f aca="false">G230/G237</f>
@@ -55510,7 +55510,7 @@
       </c>
       <c r="F240" s="15" t="n">
         <f aca="false">(F230+F232)/F237</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G240" s="15" t="n">
         <f aca="false">(G230+G232)/G237</f>
@@ -55530,7 +55530,7 @@
       </c>
       <c r="E241" s="16" t="n">
         <f aca="false">E230/fx/E221</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F241" s="16" t="n">
         <f aca="false">F230/fx/F221</f>
@@ -55538,7 +55538,7 @@
       </c>
       <c r="G241" s="16" t="n">
         <f aca="false">G230/fx/G221</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55554,11 +55554,11 @@
       </c>
       <c r="E242" s="19" t="n">
         <f aca="false">E228/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F242" s="19" t="n">
         <f aca="false">F228/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G242" s="19" t="n">
         <f aca="false">G228/fx/odm_vr</f>
@@ -55601,15 +55601,15 @@
       </c>
       <c r="E245" s="22" t="n">
         <f aca="false">($D$244+d_ai+vrd)*E228*(1-E229*(1-keep_lo))</f>
-        <v>340.781558837342</v>
+        <v>340.781558837343</v>
       </c>
       <c r="F245" s="22" t="n">
         <f aca="false">($D$244+d_ai+vrd)*F228*(1-F229*(1-keep_lo))</f>
-        <v>418.620195100263</v>
+        <v>418.620195100264</v>
       </c>
       <c r="G245" s="22" t="n">
         <f aca="false">($D$244+d_ai+vrd)*G228*(1-G229*(1-keep_lo))</f>
-        <v>445.801640221963</v>
+        <v>445.801640221964</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>472</v>
@@ -55632,7 +55632,7 @@
       </c>
       <c r="E246" s="19" t="n">
         <f aca="false">$D$244*E236+E245</f>
-        <v>838.78806631202</v>
+        <v>838.788066312021</v>
       </c>
       <c r="F246" s="19" t="n">
         <f aca="false">$D$244*F236+F245</f>
@@ -55640,7 +55640,7 @@
       </c>
       <c r="G246" s="19" t="n">
         <f aca="false">$D$244*G236+G245</f>
-        <v>980.54407725048</v>
+        <v>980.544077250481</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55779,7 +55779,7 @@
       </c>
       <c r="G251" s="19" t="n">
         <f aca="false">G246-G250</f>
-        <v>690.777296334796</v>
+        <v>690.777296334797</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55863,7 +55863,7 @@
       </c>
       <c r="G254" s="19" t="n">
         <f aca="false">G251*G253</f>
-        <v>455.913015580965</v>
+        <v>455.913015580966</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55919,7 +55919,7 @@
       </c>
       <c r="G256" s="22" t="n">
         <f aca="false">G254/G255</f>
-        <v>32.5258027549959</v>
+        <v>32.525802754996</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55935,7 +55935,7 @@
       </c>
       <c r="E257" s="15" t="n">
         <f aca="false">E256/D256-1</f>
-        <v>0.343549164282912</v>
+        <v>0.343549164282913</v>
       </c>
       <c r="F257" s="15" t="n">
         <f aca="false">F256/E256-1</f>
@@ -55943,7 +55943,7 @@
       </c>
       <c r="G257" s="15" t="n">
         <f aca="false">G256/F256-1</f>
-        <v>0.0636773744375174</v>
+        <v>0.0636773744375179</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55991,7 +55991,7 @@
       </c>
       <c r="D263" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E263" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56090,7 +56090,7 @@
       </c>
       <c r="D267" s="19" t="n">
         <f aca="false">D265*D266</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E267" s="19" t="n">
         <f aca="false">E265*E266</f>
@@ -56114,7 +56114,7 @@
       </c>
       <c r="D268" s="19" t="n">
         <f aca="false">D267*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E268" s="19" t="n">
         <f aca="false">E267*fx</f>
@@ -56205,15 +56205,15 @@
       </c>
       <c r="E272" s="19" t="n">
         <f aca="false">E268*E271</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F272" s="19" t="n">
         <f aca="false">F268*F271</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G272" s="19" t="n">
         <f aca="false">G268*G271</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56260,15 +56260,15 @@
       </c>
       <c r="E274" s="19" t="n">
         <f aca="false">E272*(1-E273)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F274" s="19" t="n">
         <f aca="false">F272*(1-F273)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G274" s="19" t="n">
         <f aca="false">G272*(1-G273)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56457,7 +56457,7 @@
       </c>
       <c r="E282" s="15" t="n">
         <f aca="false">E281/D281-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F282" s="15" t="n">
         <f aca="false">F281/E281-1</f>
@@ -56485,11 +56485,11 @@
       </c>
       <c r="E283" s="15" t="n">
         <f aca="false">E274/E281</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F283" s="15" t="n">
         <f aca="false">F274/F281</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G283" s="15" t="n">
         <f aca="false">G274/G281</f>
@@ -56517,7 +56517,7 @@
       </c>
       <c r="F284" s="15" t="n">
         <f aca="false">(F274+F276)/F281</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G284" s="15" t="n">
         <f aca="false">(G274+G276)/G281</f>
@@ -56537,7 +56537,7 @@
       </c>
       <c r="E285" s="16" t="n">
         <f aca="false">E274/fx/E265</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F285" s="16" t="n">
         <f aca="false">F274/fx/F265</f>
@@ -56545,7 +56545,7 @@
       </c>
       <c r="G285" s="16" t="n">
         <f aca="false">G274/fx/G265</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56561,11 +56561,11 @@
       </c>
       <c r="E286" s="19" t="n">
         <f aca="false">E272/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F286" s="19" t="n">
         <f aca="false">F272/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G286" s="19" t="n">
         <f aca="false">G272/fx/odm_vr</f>
@@ -56608,15 +56608,15 @@
       </c>
       <c r="E289" s="22" t="n">
         <f aca="false">($D$288+d_ai+vrd)*E272*(1-E273*(1-keep_hi))</f>
-        <v>351.321194677672</v>
+        <v>351.321194677673</v>
       </c>
       <c r="F289" s="22" t="n">
         <f aca="false">($D$288+d_ai+vrd)*F272*(1-F273*(1-keep_hi))</f>
-        <v>445.340633085386</v>
+        <v>445.340633085387</v>
       </c>
       <c r="G289" s="22" t="n">
         <f aca="false">($D$288+d_ai+vrd)*G272*(1-G273*(1-keep_hi))</f>
-        <v>481.947719158879</v>
+        <v>481.94771915888</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>472</v>
@@ -56639,7 +56639,7 @@
       </c>
       <c r="E290" s="19" t="n">
         <f aca="false">$D$288*E280+E289</f>
-        <v>849.32770215235</v>
+        <v>849.327702152351</v>
       </c>
       <c r="F290" s="19" t="n">
         <f aca="false">$D$288*F280+F289</f>
@@ -56667,7 +56667,7 @@
       </c>
       <c r="E291" s="14" t="n">
         <f aca="false">E290/E281</f>
-        <v>0.0618374292095398</v>
+        <v>0.0618374292095399</v>
       </c>
       <c r="F291" s="14" t="n">
         <f aca="false">F290/F281</f>
@@ -56675,7 +56675,7 @@
       </c>
       <c r="G291" s="14" t="n">
         <f aca="false">G290/G281</f>
-        <v>0.0671276510994521</v>
+        <v>0.067127651099452</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56786,7 +56786,7 @@
       </c>
       <c r="G295" s="19" t="n">
         <f aca="false">G290-G294</f>
-        <v>726.923375271712</v>
+        <v>726.923375271713</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56926,7 +56926,7 @@
       </c>
       <c r="G300" s="22" t="n">
         <f aca="false">G298/G299</f>
-        <v>34.2277698580068</v>
+        <v>34.2277698580069</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56942,15 +56942,15 @@
       </c>
       <c r="E301" s="15" t="n">
         <f aca="false">E300/D300-1</f>
-        <v>0.36882066490652</v>
+        <v>0.368820664906521</v>
       </c>
       <c r="F301" s="15" t="n">
         <f aca="false">F300/E300-1</f>
-        <v>0.184399348180445</v>
+        <v>0.184399348180444</v>
       </c>
       <c r="G301" s="15" t="n">
         <f aca="false">G300/F300-1</f>
-        <v>0.0751012013714025</v>
+        <v>0.0751012013714028</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="D307" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E307" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="D311" s="19" t="n">
         <f aca="false">D309*D310</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E311" s="19" t="n">
         <f aca="false">E309*E310</f>
@@ -57121,7 +57121,7 @@
       </c>
       <c r="D312" s="19" t="n">
         <f aca="false">D311*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E312" s="19" t="n">
         <f aca="false">E311*fx</f>
@@ -57212,15 +57212,15 @@
       </c>
       <c r="E316" s="19" t="n">
         <f aca="false">E312*E315</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F316" s="19" t="n">
         <f aca="false">F312*F315</f>
-        <v>6857.73377445529</v>
+        <v>6857.7337744553</v>
       </c>
       <c r="G316" s="19" t="n">
         <f aca="false">G312*G315</f>
-        <v>7421.44081553826</v>
+        <v>7421.44081553828</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57267,15 +57267,15 @@
       </c>
       <c r="E318" s="19" t="n">
         <f aca="false">E316*(1-E317)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F318" s="19" t="n">
         <f aca="false">F316*(1-F317)</f>
-        <v>5486.18701956423</v>
+        <v>5486.18701956424</v>
       </c>
       <c r="G318" s="19" t="n">
         <f aca="false">G316*(1-G317)</f>
-        <v>5566.0806116537</v>
+        <v>5566.08061165371</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57464,7 +57464,7 @@
       </c>
       <c r="E326" s="15" t="n">
         <f aca="false">E325/D325-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F326" s="15" t="n">
         <f aca="false">F325/E325-1</f>
@@ -57492,7 +57492,7 @@
       </c>
       <c r="E327" s="15" t="n">
         <f aca="false">E318/E325</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F327" s="15" t="n">
         <f aca="false">F318/F325</f>
@@ -57544,7 +57544,7 @@
       </c>
       <c r="E329" s="16" t="n">
         <f aca="false">E318/fx/E309</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F329" s="16" t="n">
         <f aca="false">F318/fx/F309</f>
@@ -57568,15 +57568,15 @@
       </c>
       <c r="E330" s="19" t="n">
         <f aca="false">E316/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F330" s="19" t="n">
         <f aca="false">F316/fx/odm_vr</f>
-        <v>31.74876747433</v>
+        <v>31.7487674743301</v>
       </c>
       <c r="G330" s="19" t="n">
         <f aca="false">G316/fx/odm_vr</f>
-        <v>34.3585222941586</v>
+        <v>34.3585222941587</v>
       </c>
       <c r="H330" s="4" t="s">
         <v>467</v>
@@ -57650,11 +57650,11 @@
       </c>
       <c r="F334" s="19" t="n">
         <f aca="false">$D$332*F324+F333</f>
-        <v>888.683007204024</v>
+        <v>888.683007204025</v>
       </c>
       <c r="G334" s="19" t="n">
         <f aca="false">$D$332*G324+G333</f>
-        <v>934.156609281438</v>
+        <v>934.156609281439</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57785,11 +57785,11 @@
       </c>
       <c r="E339" s="19" t="n">
         <f aca="false">E334-E338</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F339" s="19" t="n">
         <f aca="false">F334-F338</f>
-        <v>609.623348603006</v>
+        <v>609.623348603007</v>
       </c>
       <c r="G339" s="19" t="n">
         <f aca="false">G334-G338</f>
@@ -57869,15 +57869,15 @@
       </c>
       <c r="E342" s="19" t="n">
         <f aca="false">E339*E341</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F342" s="19" t="n">
         <f aca="false">F339*F341</f>
-        <v>402.351410077984</v>
+        <v>402.351410077985</v>
       </c>
       <c r="G342" s="19" t="n">
         <f aca="false">G339*G341</f>
-        <v>430.477272478598</v>
+        <v>430.477272478599</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57949,15 +57949,15 @@
       </c>
       <c r="E345" s="15" t="n">
         <f aca="false">E344/D344-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F345" s="15" t="n">
         <f aca="false">F344/E344-1</f>
-        <v>0.0744875950669239</v>
+        <v>0.0744875950669237</v>
       </c>
       <c r="G345" s="15" t="n">
         <f aca="false">G344/F344-1</f>
-        <v>0.069903725191774</v>
+        <v>0.0699037251917738</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58005,7 +58005,7 @@
       </c>
       <c r="D351" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E351" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58104,7 +58104,7 @@
       </c>
       <c r="D355" s="19" t="n">
         <f aca="false">D353*D354</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E355" s="19" t="n">
         <f aca="false">E353*E354</f>
@@ -58128,7 +58128,7 @@
       </c>
       <c r="D356" s="19" t="n">
         <f aca="false">D355*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E356" s="19" t="n">
         <f aca="false">E355*fx</f>
@@ -58219,11 +58219,11 @@
       </c>
       <c r="E360" s="19" t="n">
         <f aca="false">E356*E359</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F360" s="19" t="n">
         <f aca="false">F356*F359</f>
-        <v>9681.50650511334</v>
+        <v>9681.50650511336</v>
       </c>
       <c r="G360" s="19" t="n">
         <f aca="false">G356*G359</f>
@@ -58274,15 +58274,15 @@
       </c>
       <c r="E362" s="19" t="n">
         <f aca="false">E360*(1-E361)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F362" s="19" t="n">
         <f aca="false">F360*(1-F361)</f>
-        <v>7745.20520409068</v>
+        <v>7745.20520409069</v>
       </c>
       <c r="G362" s="19" t="n">
         <f aca="false">G360*(1-G361)</f>
-        <v>7857.99615762875</v>
+        <v>7857.99615762876</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58471,15 +58471,15 @@
       </c>
       <c r="E370" s="15" t="n">
         <f aca="false">E369/D369-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F370" s="15" t="n">
         <f aca="false">F369/E369-1</f>
-        <v>0.169924058558726</v>
+        <v>0.169924058558727</v>
       </c>
       <c r="G370" s="15" t="n">
         <f aca="false">G369/F369-1</f>
-        <v>0.0240566991913211</v>
+        <v>0.0240566991913207</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58499,7 +58499,7 @@
       </c>
       <c r="E371" s="15" t="n">
         <f aca="false">E362/E369</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F371" s="15" t="n">
         <f aca="false">F362/F369</f>
@@ -58507,7 +58507,7 @@
       </c>
       <c r="G371" s="15" t="n">
         <f aca="false">G362/G369</f>
-        <v>0.477536172106276</v>
+        <v>0.477536172106277</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58531,11 +58531,11 @@
       </c>
       <c r="F372" s="15" t="n">
         <f aca="false">(F362+F364)/F369</f>
-        <v>0.659955491629732</v>
+        <v>0.659955491629733</v>
       </c>
       <c r="G372" s="15" t="n">
         <f aca="false">(G362+G364)/G369</f>
-        <v>0.66173270907664</v>
+        <v>0.661732709076641</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58551,7 +58551,7 @@
       </c>
       <c r="E373" s="16" t="n">
         <f aca="false">E362/fx/E353</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F373" s="16" t="n">
         <f aca="false">F362/fx/F353</f>
@@ -58575,15 +58575,15 @@
       </c>
       <c r="E374" s="19" t="n">
         <f aca="false">E360/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F374" s="19" t="n">
         <f aca="false">F360/fx/odm_vr</f>
-        <v>44.8217893755247</v>
+        <v>44.8217893755248</v>
       </c>
       <c r="G374" s="19" t="n">
         <f aca="false">G360/fx/odm_vr</f>
-        <v>48.5061491211651</v>
+        <v>48.5061491211652</v>
       </c>
       <c r="H374" s="4" t="s">
         <v>467</v>
@@ -58626,11 +58626,11 @@
       </c>
       <c r="F377" s="22" t="n">
         <f aca="false">($D$376+d_ai+vrd)*F360*(1-F361*(1-keep))</f>
-        <v>523.720584508414</v>
+        <v>523.720584508415</v>
       </c>
       <c r="G377" s="22" t="n">
         <f aca="false">($D$376+d_ai+vrd)*G360*(1-G361*(1-keep))</f>
-        <v>563.878831415888</v>
+        <v>563.878831415889</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>472</v>
@@ -58792,7 +58792,7 @@
       </c>
       <c r="E383" s="19" t="n">
         <f aca="false">E378-E382</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F383" s="19" t="n">
         <f aca="false">F378-F382</f>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="G383" s="19" t="n">
         <f aca="false">G378-G382</f>
-        <v>798.380803795304</v>
+        <v>798.380803795305</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58876,7 +58876,7 @@
       </c>
       <c r="E386" s="19" t="n">
         <f aca="false">E383*E385</f>
-        <v>374.458869441786</v>
+        <v>374.458869441787</v>
       </c>
       <c r="F386" s="19" t="n">
         <f aca="false">F383*F385</f>
@@ -58940,7 +58940,7 @@
       </c>
       <c r="G388" s="22" t="n">
         <f aca="false">G386/G387</f>
-        <v>37.5924001634173</v>
+        <v>37.5924001634174</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58956,15 +58956,15 @@
       </c>
       <c r="E389" s="15" t="n">
         <f aca="false">E388/D388-1</f>
-        <v>0.360396831365317</v>
+        <v>0.360396831365319</v>
       </c>
       <c r="F389" s="15" t="n">
         <f aca="false">F388/E388-1</f>
-        <v>0.31143090636328</v>
+        <v>0.311430906363279</v>
       </c>
       <c r="G389" s="15" t="n">
         <f aca="false">G388/F388-1</f>
-        <v>0.0730117695104224</v>
+        <v>0.0730117695104233</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59012,7 +59012,7 @@
       </c>
       <c r="D395" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E395" s="22" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -59111,7 +59111,7 @@
       </c>
       <c r="D399" s="19" t="n">
         <f aca="false">D397*D398</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E399" s="19" t="n">
         <f aca="false">E397*E398</f>
@@ -59135,7 +59135,7 @@
       </c>
       <c r="D400" s="19" t="n">
         <f aca="false">D399*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E400" s="19" t="n">
         <f aca="false">E399*fx</f>
@@ -59226,15 +59226,15 @@
       </c>
       <c r="E404" s="19" t="n">
         <f aca="false">E400*E403</f>
-        <v>5091.71059778255</v>
+        <v>5091.71059778256</v>
       </c>
       <c r="F404" s="19" t="n">
         <f aca="false">F400*F403</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G404" s="19" t="n">
         <f aca="false">G400*G403</f>
-        <v>6984.88547344778</v>
+        <v>6984.88547344779</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59285,11 +59285,11 @@
       </c>
       <c r="F406" s="19" t="n">
         <f aca="false">F404*(1-F405)</f>
-        <v>5163.47013606045</v>
+        <v>5163.47013606046</v>
       </c>
       <c r="G406" s="19" t="n">
         <f aca="false">G404*(1-G405)</f>
-        <v>5238.66410508583</v>
+        <v>5238.66410508584</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59486,7 +59486,7 @@
       </c>
       <c r="G414" s="15" t="n">
         <f aca="false">G413/F413-1</f>
-        <v>0.0258740825857917</v>
+        <v>0.0258740825857919</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59514,7 +59514,7 @@
       </c>
       <c r="G415" s="15" t="n">
         <f aca="false">G406/G413</f>
-        <v>0.378626775001188</v>
+        <v>0.378626775001189</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59542,7 +59542,7 @@
       </c>
       <c r="G416" s="15" t="n">
         <f aca="false">(G406+G408)/G413</f>
-        <v>0.59769418235129</v>
+        <v>0.597694182351291</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59558,7 +59558,7 @@
       </c>
       <c r="E417" s="16" t="n">
         <f aca="false">E406/fx/E397</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F417" s="16" t="n">
         <f aca="false">F406/fx/F397</f>
@@ -59566,7 +59566,7 @@
       </c>
       <c r="G417" s="16" t="n">
         <f aca="false">G406/fx/G397</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59590,7 +59590,7 @@
       </c>
       <c r="G418" s="19" t="n">
         <f aca="false">G404/fx/odm_vr</f>
-        <v>32.3374327474434</v>
+        <v>32.3374327474435</v>
       </c>
       <c r="H418" s="4" t="s">
         <v>467</v>
@@ -59660,11 +59660,11 @@
       </c>
       <c r="E422" s="19" t="n">
         <f aca="false">$D$420*E412+E421</f>
-        <v>776.252893659394</v>
+        <v>776.252893659395</v>
       </c>
       <c r="F422" s="19" t="n">
         <f aca="false">$D$420*F412+F421</f>
-        <v>866.86131618284</v>
+        <v>866.861316182841</v>
       </c>
       <c r="G422" s="19" t="n">
         <f aca="false">$D$420*G412+G421</f>
@@ -59883,11 +59883,11 @@
       </c>
       <c r="E430" s="19" t="n">
         <f aca="false">E427*E429</f>
-        <v>335.4601235334</v>
+        <v>335.460123533401</v>
       </c>
       <c r="F430" s="19" t="n">
         <f aca="false">F427*F429</f>
-        <v>390.216486007329</v>
+        <v>390.21648600733</v>
       </c>
       <c r="G430" s="19" t="n">
         <f aca="false">G427*G429</f>
@@ -59939,7 +59939,7 @@
       </c>
       <c r="E432" s="22" t="n">
         <f aca="false">E430/E431</f>
-        <v>23.9324376302572</v>
+        <v>23.9324376302573</v>
       </c>
       <c r="F432" s="22" t="n">
         <f aca="false">F430/F431</f>
@@ -59963,7 +59963,7 @@
       </c>
       <c r="E433" s="15" t="n">
         <f aca="false">E432/D432-1</f>
-        <v>0.218715662375842</v>
+        <v>0.218715662375843</v>
       </c>
       <c r="F433" s="15" t="n">
         <f aca="false">F432/E432-1</f>
@@ -59971,7 +59971,7 @@
       </c>
       <c r="G433" s="15" t="n">
         <f aca="false">G432/F432-1</f>
-        <v>0.0692577179207541</v>
+        <v>0.0692577179207543</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60019,7 +60019,7 @@
       </c>
       <c r="D439" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E439" s="22" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -60118,7 +60118,7 @@
       </c>
       <c r="D443" s="19" t="n">
         <f aca="false">D441*D442</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E443" s="19" t="n">
         <f aca="false">E441*E442</f>
@@ -60142,7 +60142,7 @@
       </c>
       <c r="D444" s="19" t="n">
         <f aca="false">D443*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E444" s="19" t="n">
         <f aca="false">E443*fx</f>
@@ -60233,11 +60233,11 @@
       </c>
       <c r="E448" s="19" t="n">
         <f aca="false">E444*E447</f>
-        <v>7637.56589667383</v>
+        <v>7637.56589667384</v>
       </c>
       <c r="F448" s="19" t="n">
         <f aca="false">F444*F447</f>
-        <v>9681.50650511335</v>
+        <v>9681.50650511336</v>
       </c>
       <c r="G448" s="19" t="n">
         <f aca="false">G444*G447</f>
@@ -60288,15 +60288,15 @@
       </c>
       <c r="E450" s="19" t="n">
         <f aca="false">E448*(1-E449)</f>
-        <v>6873.80930700645</v>
+        <v>6873.80930700646</v>
       </c>
       <c r="F450" s="19" t="n">
         <f aca="false">F448*(1-F449)</f>
-        <v>7745.20520409068</v>
+        <v>7745.20520409069</v>
       </c>
       <c r="G450" s="19" t="n">
         <f aca="false">G448*(1-G449)</f>
-        <v>7857.99615762875</v>
+        <v>7857.99615762876</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60461,7 +60461,7 @@
       </c>
       <c r="E457" s="19" t="n">
         <f aca="false">E450+E456</f>
-        <v>14880.4830664064</v>
+        <v>14880.4830664065</v>
       </c>
       <c r="F457" s="19" t="n">
         <f aca="false">F450+F456</f>
@@ -60485,7 +60485,7 @@
       </c>
       <c r="E458" s="15" t="n">
         <f aca="false">E457/D457-1</f>
-        <v>0.334484504062418</v>
+        <v>0.334484504062419</v>
       </c>
       <c r="F458" s="15" t="n">
         <f aca="false">F457/E457-1</f>
@@ -60493,7 +60493,7 @@
       </c>
       <c r="G458" s="15" t="n">
         <f aca="false">G457/F457-1</f>
-        <v>0.0240566991913209</v>
+        <v>0.0240566991913207</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60521,7 +60521,7 @@
       </c>
       <c r="G459" s="15" t="n">
         <f aca="false">G450/G457</f>
-        <v>0.477536172106276</v>
+        <v>0.477536172106277</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60545,11 +60545,11 @@
       </c>
       <c r="F460" s="15" t="n">
         <f aca="false">(F450+F452)/F457</f>
-        <v>0.659955491629732</v>
+        <v>0.659955491629733</v>
       </c>
       <c r="G460" s="15" t="n">
         <f aca="false">(G450+G452)/G457</f>
-        <v>0.66173270907664</v>
+        <v>0.661732709076641</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60565,7 +60565,7 @@
       </c>
       <c r="E461" s="16" t="n">
         <f aca="false">E450/fx/E441</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F461" s="16" t="n">
         <f aca="false">F450/fx/F441</f>
@@ -60573,7 +60573,7 @@
       </c>
       <c r="G461" s="16" t="n">
         <f aca="false">G450/fx/G441</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60597,7 +60597,7 @@
       </c>
       <c r="G462" s="19" t="n">
         <f aca="false">G448/fx/odm_vr</f>
-        <v>48.5061491211651</v>
+        <v>48.5061491211652</v>
       </c>
       <c r="H462" s="4" t="s">
         <v>467</v>
@@ -60636,15 +60636,15 @@
       </c>
       <c r="E465" s="22" t="n">
         <f aca="false">($D$464+d_ai+vrd)*E448*(1-E449*(1-keep))</f>
-        <v>417.369579277075</v>
+        <v>417.369579277076</v>
       </c>
       <c r="F465" s="22" t="n">
         <f aca="false">($D$464+d_ai+vrd)*F448*(1-F449*(1-keep))</f>
-        <v>523.720584508414</v>
+        <v>523.720584508415</v>
       </c>
       <c r="G465" s="22" t="n">
         <f aca="false">($D$464+d_ai+vrd)*G448*(1-G449*(1-keep))</f>
-        <v>563.878831415888</v>
+        <v>563.878831415889</v>
       </c>
       <c r="H465" s="4" t="s">
         <v>472</v>
@@ -60667,7 +60667,7 @@
       </c>
       <c r="E466" s="19" t="n">
         <f aca="false">$D$464*E456+E465</f>
-        <v>915.376086751753</v>
+        <v>915.376086751754</v>
       </c>
       <c r="F466" s="19" t="n">
         <f aca="false">$D$464*F456+F465</f>
@@ -60754,7 +60754,7 @@
       </c>
       <c r="F469" s="19" t="n">
         <f aca="false">E469*(1+MAX(0,phi*F458))</f>
-        <v>298.153732084499</v>
+        <v>298.1537320845</v>
       </c>
       <c r="G469" s="19" t="n">
         <f aca="false">F469*(1+MAX(0,phi*G458))</f>
@@ -60782,7 +60782,7 @@
       </c>
       <c r="F470" s="19" t="n">
         <f aca="false">F469+0*F457</f>
-        <v>298.153732084499</v>
+        <v>298.1537320845</v>
       </c>
       <c r="G470" s="19" t="n">
         <f aca="false">G469+0*G457</f>
@@ -60806,15 +60806,15 @@
       </c>
       <c r="E471" s="19" t="n">
         <f aca="false">E466-E470</f>
-        <v>626.450932348746</v>
+        <v>626.450932348747</v>
       </c>
       <c r="F471" s="19" t="n">
         <f aca="false">F466-F470</f>
-        <v>743.281112267812</v>
+        <v>743.281112267813</v>
       </c>
       <c r="G471" s="19" t="n">
         <f aca="false">G466-G470</f>
-        <v>797.598498501695</v>
+        <v>797.598498501696</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60842,7 +60842,7 @@
       </c>
       <c r="G472" s="14" t="n">
         <f aca="false">G471/G457</f>
-        <v>0.0484706439417691</v>
+        <v>0.0484706439417692</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60898,7 +60898,7 @@
       </c>
       <c r="G474" s="19" t="n">
         <f aca="false">G471*G473</f>
-        <v>526.415009011119</v>
+        <v>526.41500901112</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60970,7 +60970,7 @@
       </c>
       <c r="E477" s="15" t="n">
         <f aca="false">E476/D476-1</f>
-        <v>0.502078000354793</v>
+        <v>0.502078000354794</v>
       </c>
       <c r="F477" s="15" t="n">
         <f aca="false">F476/E476-1</f>
@@ -60978,7 +60978,7 @@
       </c>
       <c r="G477" s="15" t="n">
         <f aca="false">G476/F476-1</f>
-        <v>0.0730778508122669</v>
+        <v>0.0730778508122676</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61026,7 +61026,7 @@
       </c>
       <c r="D483" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E483" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61125,7 +61125,7 @@
       </c>
       <c r="D487" s="19" t="n">
         <f aca="false">D485*D486</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E487" s="19" t="n">
         <f aca="false">E485*E486</f>
@@ -61149,7 +61149,7 @@
       </c>
       <c r="D488" s="19" t="n">
         <f aca="false">D487*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E488" s="19" t="n">
         <f aca="false">E487*fx</f>
@@ -61240,15 +61240,15 @@
       </c>
       <c r="E492" s="19" t="n">
         <f aca="false">E488*E491</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F492" s="19" t="n">
         <f aca="false">F488*F491</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G492" s="19" t="n">
         <f aca="false">G488*G491</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61295,15 +61295,15 @@
       </c>
       <c r="E494" s="19" t="n">
         <f aca="false">E492*(1-E493)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F494" s="19" t="n">
         <f aca="false">F492*(1-F493)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G494" s="19" t="n">
         <f aca="false">G492*(1-G493)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="E502" s="15" t="n">
         <f aca="false">E501/D501-1</f>
-        <v>0.198743753385348</v>
+        <v>0.198743753385349</v>
       </c>
       <c r="F502" s="15" t="n">
         <f aca="false">F501/E501-1</f>
@@ -61500,7 +61500,7 @@
       </c>
       <c r="G502" s="15" t="n">
         <f aca="false">G501/F501-1</f>
-        <v>0.00503454566356165</v>
+        <v>0.00503454566356187</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61524,11 +61524,11 @@
       </c>
       <c r="F503" s="15" t="n">
         <f aca="false">F494/F501</f>
-        <v>0.457924371374064</v>
+        <v>0.457924371374065</v>
       </c>
       <c r="G503" s="15" t="n">
         <f aca="false">G494/G501</f>
-        <v>0.462265680291901</v>
+        <v>0.462265680291902</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61552,7 +61552,7 @@
       </c>
       <c r="F504" s="15" t="n">
         <f aca="false">(F494+F496)/F501</f>
-        <v>0.660796884552524</v>
+        <v>0.660796884552525</v>
       </c>
       <c r="G504" s="15" t="n">
         <f aca="false">(G494+G496)/G501</f>
@@ -61572,7 +61572,7 @@
       </c>
       <c r="E505" s="16" t="n">
         <f aca="false">E494/fx/E485</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F505" s="16" t="n">
         <f aca="false">F494/fx/F485</f>
@@ -61580,7 +61580,7 @@
       </c>
       <c r="G505" s="16" t="n">
         <f aca="false">G494/fx/G485</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61596,11 +61596,11 @@
       </c>
       <c r="E506" s="19" t="n">
         <f aca="false">E492/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F506" s="19" t="n">
         <f aca="false">F492/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G506" s="19" t="n">
         <f aca="false">G492/fx/odm_vr</f>
@@ -61647,11 +61647,11 @@
       </c>
       <c r="F509" s="22" t="n">
         <f aca="false">($D$508+d_ai+vrd)*F492*(1-F493*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G509" s="22" t="n">
         <f aca="false">($D$508+d_ai+vrd)*G492*(1-G493*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H509" s="4" t="s">
         <v>472</v>
@@ -61678,7 +61678,7 @@
       </c>
       <c r="F510" s="19" t="n">
         <f aca="false">$D$508*F500+F509</f>
-        <v>911.660365588869</v>
+        <v>911.66036558887</v>
       </c>
       <c r="G510" s="19" t="n">
         <f aca="false">$D$508*G500+G509</f>
@@ -61821,7 +61821,7 @@
       </c>
       <c r="G515" s="19" t="n">
         <f aca="false">G510-G514</f>
-        <v>662.046182604169</v>
+        <v>662.04618260417</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61977,7 +61977,7 @@
       </c>
       <c r="E521" s="15" t="n">
         <f aca="false">E520/D520-1</f>
-        <v>0.313583375183364</v>
+        <v>0.313583375183365</v>
       </c>
       <c r="F521" s="15" t="n">
         <f aca="false">F520/E520-1</f>
@@ -61985,7 +61985,7 @@
       </c>
       <c r="G521" s="15" t="n">
         <f aca="false">G520/F520-1</f>
-        <v>0.0499010973851151</v>
+        <v>0.0499010973851155</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62033,7 +62033,7 @@
       </c>
       <c r="D527" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E527" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62132,7 +62132,7 @@
       </c>
       <c r="D531" s="19" t="n">
         <f aca="false">D529*D530</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E531" s="19" t="n">
         <f aca="false">E529*E530</f>
@@ -62156,7 +62156,7 @@
       </c>
       <c r="D532" s="19" t="n">
         <f aca="false">D531*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E532" s="19" t="n">
         <f aca="false">E531*fx</f>
@@ -62247,15 +62247,15 @@
       </c>
       <c r="E536" s="19" t="n">
         <f aca="false">E532*E535</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F536" s="19" t="n">
         <f aca="false">F532*F535</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G536" s="19" t="n">
         <f aca="false">G532*G535</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62302,15 +62302,15 @@
       </c>
       <c r="E538" s="19" t="n">
         <f aca="false">E536*(1-E537)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F538" s="19" t="n">
         <f aca="false">F536*(1-F537)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G538" s="19" t="n">
         <f aca="false">G536*(1-G537)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62499,7 +62499,7 @@
       </c>
       <c r="E546" s="15" t="n">
         <f aca="false">E545/D545-1</f>
-        <v>0.246743753385348</v>
+        <v>0.246743753385349</v>
       </c>
       <c r="F546" s="15" t="n">
         <f aca="false">F545/E545-1</f>
@@ -62527,11 +62527,11 @@
       </c>
       <c r="E547" s="15" t="n">
         <f aca="false">E538/E545</f>
-        <v>0.412036356300532</v>
+        <v>0.412036356300533</v>
       </c>
       <c r="F547" s="15" t="n">
         <f aca="false">F538/F545</f>
-        <v>0.427638345807247</v>
+        <v>0.427638345807248</v>
       </c>
       <c r="G547" s="15" t="n">
         <f aca="false">G538/G545</f>
@@ -62579,7 +62579,7 @@
       </c>
       <c r="E549" s="16" t="n">
         <f aca="false">E538/fx/E529</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F549" s="16" t="n">
         <f aca="false">F538/fx/F529</f>
@@ -62587,7 +62587,7 @@
       </c>
       <c r="G549" s="16" t="n">
         <f aca="false">G538/fx/G529</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62603,11 +62603,11 @@
       </c>
       <c r="E550" s="19" t="n">
         <f aca="false">E536/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F550" s="19" t="n">
         <f aca="false">F536/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G550" s="19" t="n">
         <f aca="false">G536/fx/odm_vr</f>
@@ -62654,11 +62654,11 @@
       </c>
       <c r="F553" s="22" t="n">
         <f aca="false">($D$552+d_ai+vrd)*F536*(1-F537*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G553" s="22" t="n">
         <f aca="false">($D$552+d_ai+vrd)*G536*(1-G537*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H553" s="4" t="s">
         <v>472</v>
@@ -62685,7 +62685,7 @@
       </c>
       <c r="F554" s="19" t="n">
         <f aca="false">$D$552*F544+F553</f>
-        <v>973.748191544433</v>
+        <v>973.748191544434</v>
       </c>
       <c r="G554" s="19" t="n">
         <f aca="false">$D$552*G544+G553</f>
@@ -62820,7 +62820,7 @@
       </c>
       <c r="E559" s="19" t="n">
         <f aca="false">E554-E558</f>
-        <v>576.236396948596</v>
+        <v>576.236396948597</v>
       </c>
       <c r="F559" s="19" t="n">
         <f aca="false">F554-F558</f>
@@ -62828,7 +62828,7 @@
       </c>
       <c r="G559" s="19" t="n">
         <f aca="false">G554-G558</f>
-        <v>740.540165448771</v>
+        <v>740.540165448772</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62908,11 +62908,11 @@
       </c>
       <c r="F562" s="19" t="n">
         <f aca="false">F559*F561</f>
-        <v>451.554319872878</v>
+        <v>451.554319872879</v>
       </c>
       <c r="G562" s="19" t="n">
         <f aca="false">G559*G561</f>
-        <v>488.756509196189</v>
+        <v>488.75650919619</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62984,7 +62984,7 @@
       </c>
       <c r="E565" s="15" t="n">
         <f aca="false">E564/D564-1</f>
-        <v>0.381675675084388</v>
+        <v>0.381675675084389</v>
       </c>
       <c r="F565" s="15" t="n">
         <f aca="false">F564/E564-1</f>
@@ -62992,7 +62992,7 @@
       </c>
       <c r="G565" s="15" t="n">
         <f aca="false">G564/F564-1</f>
-        <v>0.082386963618871</v>
+        <v>0.0823869636188712</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63040,7 +63040,7 @@
       </c>
       <c r="D571" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E571" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -63139,7 +63139,7 @@
       </c>
       <c r="D575" s="19" t="n">
         <f aca="false">D573*D574</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E575" s="19" t="n">
         <f aca="false">E573*E574</f>
@@ -63163,7 +63163,7 @@
       </c>
       <c r="D576" s="19" t="n">
         <f aca="false">D575*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E576" s="19" t="n">
         <f aca="false">E575*fx</f>
@@ -63254,15 +63254,15 @@
       </c>
       <c r="E580" s="19" t="n">
         <f aca="false">E576*E579</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F580" s="19" t="n">
         <f aca="false">F576*F579</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G580" s="19" t="n">
         <f aca="false">G576*G579</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63309,15 +63309,15 @@
       </c>
       <c r="E582" s="19" t="n">
         <f aca="false">E580*(1-E581)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F582" s="19" t="n">
         <f aca="false">F580*(1-F581)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G582" s="19" t="n">
         <f aca="false">G580*(1-G581)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63506,7 +63506,7 @@
       </c>
       <c r="E590" s="15" t="n">
         <f aca="false">E589/D589-1</f>
-        <v>0.206303753385348</v>
+        <v>0.206303753385349</v>
       </c>
       <c r="F590" s="15" t="n">
         <f aca="false">F589/E589-1</f>
@@ -63514,7 +63514,7 @@
       </c>
       <c r="G590" s="15" t="n">
         <f aca="false">G589/F589-1</f>
-        <v>0.00592393935114166</v>
+        <v>0.00592393935114188</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63542,7 +63542,7 @@
       </c>
       <c r="G591" s="15" t="n">
         <f aca="false">G582/G589</f>
-        <v>0.459593650364864</v>
+        <v>0.459593650364865</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63586,7 +63586,7 @@
       </c>
       <c r="E593" s="16" t="n">
         <f aca="false">E582/fx/E573</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F593" s="16" t="n">
         <f aca="false">F582/fx/F573</f>
@@ -63594,7 +63594,7 @@
       </c>
       <c r="G593" s="16" t="n">
         <f aca="false">G582/fx/G573</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63610,11 +63610,11 @@
       </c>
       <c r="E594" s="19" t="n">
         <f aca="false">E580/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F594" s="19" t="n">
         <f aca="false">F580/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G594" s="19" t="n">
         <f aca="false">G580/fx/odm_vr</f>
@@ -63661,11 +63661,11 @@
       </c>
       <c r="F597" s="22" t="n">
         <f aca="false">($D$596+d_ai+vrd)*F580*(1-F581*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G597" s="22" t="n">
         <f aca="false">($D$596+d_ai+vrd)*G580*(1-G581*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H597" s="4" t="s">
         <v>472</v>
@@ -63692,11 +63692,11 @@
       </c>
       <c r="F598" s="19" t="n">
         <f aca="false">$D$596*F588+F597</f>
-        <v>915.977661154197</v>
+        <v>915.977661154198</v>
       </c>
       <c r="G598" s="19" t="n">
         <f aca="false">$D$596*G588+G597</f>
-        <v>948.815607864467</v>
+        <v>948.815607864468</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63831,7 +63831,7 @@
       </c>
       <c r="F603" s="19" t="n">
         <f aca="false">F598-F602</f>
-        <v>634.269264761347</v>
+        <v>634.269264761348</v>
       </c>
       <c r="G603" s="19" t="n">
         <f aca="false">G598-G602</f>
@@ -63919,7 +63919,7 @@
       </c>
       <c r="G606" s="19" t="n">
         <f aca="false">G603*G605</f>
-        <v>439.850190179163</v>
+        <v>439.850190179164</v>
       </c>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63991,7 +63991,7 @@
       </c>
       <c r="E609" s="15" t="n">
         <f aca="false">E608/D608-1</f>
-        <v>0.324307912417775</v>
+        <v>0.324307912417776</v>
       </c>
       <c r="F609" s="15" t="n">
         <f aca="false">F608/E608-1</f>
@@ -63999,7 +63999,7 @@
       </c>
       <c r="G609" s="15" t="n">
         <f aca="false">G608/F608-1</f>
-        <v>0.0507204417991136</v>
+        <v>0.0507204417991141</v>
       </c>
     </row>
     <row r="612" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64047,7 +64047,7 @@
       </c>
       <c r="D615" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E615" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="D619" s="19" t="n">
         <f aca="false">D617*D618</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E619" s="19" t="n">
         <f aca="false">E617*E618</f>
@@ -64170,7 +64170,7 @@
       </c>
       <c r="D620" s="19" t="n">
         <f aca="false">D619*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E620" s="19" t="n">
         <f aca="false">E619*fx</f>
@@ -64261,15 +64261,15 @@
       </c>
       <c r="E624" s="19" t="n">
         <f aca="false">E620*E623</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F624" s="19" t="n">
         <f aca="false">F620*F623</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G624" s="19" t="n">
         <f aca="false">G620*G623</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64316,15 +64316,15 @@
       </c>
       <c r="E626" s="19" t="n">
         <f aca="false">E624*(1-E625)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F626" s="19" t="n">
         <f aca="false">F624*(1-F625)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G626" s="19" t="n">
         <f aca="false">G624*(1-G625)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64513,7 +64513,7 @@
       </c>
       <c r="E634" s="15" t="n">
         <f aca="false">E633/D633-1</f>
-        <v>0.259303753385348</v>
+        <v>0.259303753385349</v>
       </c>
       <c r="F634" s="15" t="n">
         <f aca="false">F633/E633-1</f>
@@ -64541,15 +64541,15 @@
       </c>
       <c r="E635" s="15" t="n">
         <f aca="false">E626/E633</f>
-        <v>0.407926802413138</v>
+        <v>0.407926802413139</v>
       </c>
       <c r="F635" s="15" t="n">
         <f aca="false">F626/F633</f>
-        <v>0.417368707050803</v>
+        <v>0.417368707050804</v>
       </c>
       <c r="G635" s="15" t="n">
         <f aca="false">G626/G633</f>
-        <v>0.404406625887898</v>
+        <v>0.404406625887899</v>
       </c>
     </row>
     <row r="636" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64593,7 +64593,7 @@
       </c>
       <c r="E637" s="16" t="n">
         <f aca="false">E626/fx/E617</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F637" s="16" t="n">
         <f aca="false">F626/fx/F617</f>
@@ -64601,7 +64601,7 @@
       </c>
       <c r="G637" s="16" t="n">
         <f aca="false">G626/fx/G617</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64617,11 +64617,11 @@
       </c>
       <c r="E638" s="19" t="n">
         <f aca="false">E624/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F638" s="19" t="n">
         <f aca="false">F624/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G638" s="19" t="n">
         <f aca="false">G624/fx/odm_vr</f>
@@ -64668,11 +64668,11 @@
       </c>
       <c r="F641" s="22" t="n">
         <f aca="false">($D$640+d_ai+vrd)*F624*(1-F625*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G641" s="22" t="n">
         <f aca="false">($D$640+d_ai+vrd)*G624*(1-G625*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H641" s="4" t="s">
         <v>472</v>
@@ -64699,7 +64699,7 @@
       </c>
       <c r="F642" s="19" t="n">
         <f aca="false">$D$640*F632+F641</f>
-        <v>996.847193174067</v>
+        <v>996.847193174068</v>
       </c>
       <c r="G642" s="19" t="n">
         <f aca="false">$D$640*G632+G641</f>
@@ -64998,7 +64998,7 @@
       </c>
       <c r="E653" s="15" t="n">
         <f aca="false">E652/D652-1</f>
-        <v>0.399493160225155</v>
+        <v>0.399493160225156</v>
       </c>
       <c r="F653" s="15" t="n">
         <f aca="false">F652/E652-1</f>
@@ -65006,7 +65006,7 @@
       </c>
       <c r="G653" s="15" t="n">
         <f aca="false">G652/F652-1</f>
-        <v>0.0957036525610238</v>
+        <v>0.095703652561024</v>
       </c>
     </row>
     <row r="656" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65054,7 +65054,7 @@
       </c>
       <c r="D659" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E659" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -65153,7 +65153,7 @@
       </c>
       <c r="D663" s="19" t="n">
         <f aca="false">D661*D662</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E663" s="19" t="n">
         <f aca="false">E661*E662</f>
@@ -65177,7 +65177,7 @@
       </c>
       <c r="D664" s="19" t="n">
         <f aca="false">D663*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E664" s="19" t="n">
         <f aca="false">E663*fx</f>
@@ -65268,15 +65268,15 @@
       </c>
       <c r="E668" s="19" t="n">
         <f aca="false">E664*E667</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F668" s="19" t="n">
         <f aca="false">F664*F667</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G668" s="19" t="n">
         <f aca="false">G664*G667</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="669" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65323,15 +65323,15 @@
       </c>
       <c r="E670" s="19" t="n">
         <f aca="false">E668*(1-E669)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F670" s="19" t="n">
         <f aca="false">F668*(1-F669)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G670" s="19" t="n">
         <f aca="false">G668*(1-G669)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65520,7 +65520,7 @@
       </c>
       <c r="E678" s="15" t="n">
         <f aca="false">E677/D677-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F678" s="15" t="n">
         <f aca="false">F677/E677-1</f>
@@ -65548,11 +65548,11 @@
       </c>
       <c r="E679" s="15" t="n">
         <f aca="false">E670/E677</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F679" s="15" t="n">
         <f aca="false">F670/F677</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G679" s="15" t="n">
         <f aca="false">G670/G677</f>
@@ -65580,7 +65580,7 @@
       </c>
       <c r="F680" s="15" t="n">
         <f aca="false">(F670+F672)/F677</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G680" s="15" t="n">
         <f aca="false">(G670+G672)/G677</f>
@@ -65600,7 +65600,7 @@
       </c>
       <c r="E681" s="16" t="n">
         <f aca="false">E670/fx/E661</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F681" s="16" t="n">
         <f aca="false">F670/fx/F661</f>
@@ -65608,7 +65608,7 @@
       </c>
       <c r="G681" s="16" t="n">
         <f aca="false">G670/fx/G661</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65624,11 +65624,11 @@
       </c>
       <c r="E682" s="19" t="n">
         <f aca="false">E668/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F682" s="19" t="n">
         <f aca="false">F668/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G682" s="19" t="n">
         <f aca="false">G668/fx/odm_vr</f>
@@ -65671,15 +65671,15 @@
       </c>
       <c r="E685" s="22" t="n">
         <f aca="false">($D$684+d_ai_lo+vrd)*E668*(1-E669*(1-keep))</f>
-        <v>304.83521821326</v>
+        <v>304.835218213261</v>
       </c>
       <c r="F685" s="22" t="n">
         <f aca="false">($D$684+d_ai_lo+vrd)*F668*(1-F669*(1-keep))</f>
-        <v>382.511056359032</v>
+        <v>382.511056359033</v>
       </c>
       <c r="G685" s="22" t="n">
         <f aca="false">($D$684+d_ai_lo+vrd)*G668*(1-G669*(1-keep))</f>
-        <v>411.841531235293</v>
+        <v>411.841531235294</v>
       </c>
       <c r="H685" s="4" t="s">
         <v>472</v>
@@ -65702,7 +65702,7 @@
       </c>
       <c r="E686" s="19" t="n">
         <f aca="false">$D$684*E676+E685</f>
-        <v>828.30294824283</v>
+        <v>828.302948242831</v>
       </c>
       <c r="F686" s="19" t="n">
         <f aca="false">$D$684*F676+F685</f>
@@ -65849,7 +65849,7 @@
       </c>
       <c r="G691" s="19" t="n">
         <f aca="false">G686-G690</f>
-        <v>684.156581501365</v>
+        <v>684.156581501366</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65933,7 +65933,7 @@
       </c>
       <c r="G694" s="19" t="n">
         <f aca="false">G691*G693</f>
-        <v>451.543343790901</v>
+        <v>451.543343790902</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65985,7 +65985,7 @@
       </c>
       <c r="F696" s="22" t="n">
         <f aca="false">F694/F695</f>
-        <v>30.1247127690198</v>
+        <v>30.1247127690199</v>
       </c>
       <c r="G696" s="22" t="n">
         <f aca="false">G694/G695</f>
@@ -66005,7 +66005,7 @@
       </c>
       <c r="E697" s="15" t="n">
         <f aca="false">E696/D696-1</f>
-        <v>0.318408384104322</v>
+        <v>0.318408384104323</v>
       </c>
       <c r="F697" s="15" t="n">
         <f aca="false">F696/E696-1</f>
@@ -66013,7 +66013,7 @@
       </c>
       <c r="G697" s="15" t="n">
         <f aca="false">G696/F696-1</f>
-        <v>0.0693566221398212</v>
+        <v>0.0693566221398216</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66061,7 +66061,7 @@
       </c>
       <c r="D703" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E703" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -66160,7 +66160,7 @@
       </c>
       <c r="D707" s="19" t="n">
         <f aca="false">D705*D706</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E707" s="19" t="n">
         <f aca="false">E705*E706</f>
@@ -66184,7 +66184,7 @@
       </c>
       <c r="D708" s="19" t="n">
         <f aca="false">D707*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E708" s="19" t="n">
         <f aca="false">E707*fx</f>
@@ -66275,15 +66275,15 @@
       </c>
       <c r="E712" s="19" t="n">
         <f aca="false">E708*E711</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F712" s="19" t="n">
         <f aca="false">F708*F711</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G712" s="19" t="n">
         <f aca="false">G708*G711</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66330,15 +66330,15 @@
       </c>
       <c r="E714" s="19" t="n">
         <f aca="false">E712*(1-E713)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F714" s="19" t="n">
         <f aca="false">F712*(1-F713)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G714" s="19" t="n">
         <f aca="false">G712*(1-G713)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66527,7 +66527,7 @@
       </c>
       <c r="E722" s="15" t="n">
         <f aca="false">E721/D721-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F722" s="15" t="n">
         <f aca="false">F721/E721-1</f>
@@ -66555,11 +66555,11 @@
       </c>
       <c r="E723" s="15" t="n">
         <f aca="false">E714/E721</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F723" s="15" t="n">
         <f aca="false">F714/F721</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G723" s="15" t="n">
         <f aca="false">G714/G721</f>
@@ -66587,7 +66587,7 @@
       </c>
       <c r="F724" s="15" t="n">
         <f aca="false">(F714+F716)/F721</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G724" s="15" t="n">
         <f aca="false">(G714+G716)/G721</f>
@@ -66607,7 +66607,7 @@
       </c>
       <c r="E725" s="16" t="n">
         <f aca="false">E714/fx/E705</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F725" s="16" t="n">
         <f aca="false">F714/fx/F705</f>
@@ -66615,7 +66615,7 @@
       </c>
       <c r="G725" s="16" t="n">
         <f aca="false">G714/fx/G705</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66631,11 +66631,11 @@
       </c>
       <c r="E726" s="19" t="n">
         <f aca="false">E712/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F726" s="19" t="n">
         <f aca="false">F712/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G726" s="19" t="n">
         <f aca="false">G712/fx/odm_vr</f>
@@ -66686,7 +66686,7 @@
       </c>
       <c r="G729" s="22" t="n">
         <f aca="false">($D$728+d_ai_hi+vrd)*G712*(1-G713*(1-keep))</f>
-        <v>527.956521124521</v>
+        <v>527.956521124522</v>
       </c>
       <c r="H729" s="4" t="s">
         <v>472</v>
@@ -66713,7 +66713,7 @@
       </c>
       <c r="F730" s="19" t="n">
         <f aca="false">$D$728*F720+F729</f>
-        <v>981.602037616083</v>
+        <v>981.602037616084</v>
       </c>
       <c r="G730" s="19" t="n">
         <f aca="false">$D$728*G720+G729</f>
@@ -66848,15 +66848,15 @@
       </c>
       <c r="E735" s="19" t="n">
         <f aca="false">E730-E734</f>
-        <v>584.873465359389</v>
+        <v>584.87346535939</v>
       </c>
       <c r="F735" s="19" t="n">
         <f aca="false">F730-F734</f>
-        <v>694.691282879972</v>
+        <v>694.691282879973</v>
       </c>
       <c r="G735" s="19" t="n">
         <f aca="false">G730-G734</f>
-        <v>745.592783084114</v>
+        <v>745.592783084115</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66940,7 +66940,7 @@
       </c>
       <c r="G738" s="19" t="n">
         <f aca="false">G735*G737</f>
-        <v>492.091236835515</v>
+        <v>492.091236835516</v>
       </c>
     </row>
     <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67012,7 +67012,7 @@
       </c>
       <c r="E741" s="15" t="n">
         <f aca="false">E740/D740-1</f>
-        <v>0.402385278626312</v>
+        <v>0.402385278626313</v>
       </c>
       <c r="F741" s="15" t="n">
         <f aca="false">F740/E740-1</f>
@@ -67020,7 +67020,7 @@
       </c>
       <c r="G741" s="15" t="n">
         <f aca="false">G740/F740-1</f>
-        <v>0.0732721159147414</v>
+        <v>0.0732721159147416</v>
       </c>
     </row>
     <row r="744" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67068,7 +67068,7 @@
       </c>
       <c r="D747" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E747" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -67167,7 +67167,7 @@
       </c>
       <c r="D751" s="19" t="n">
         <f aca="false">D749*D750</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E751" s="19" t="n">
         <f aca="false">E749*E750</f>
@@ -67191,7 +67191,7 @@
       </c>
       <c r="D752" s="19" t="n">
         <f aca="false">D751*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E752" s="19" t="n">
         <f aca="false">E751*fx</f>
@@ -67282,15 +67282,15 @@
       </c>
       <c r="E756" s="19" t="n">
         <f aca="false">E752*E755</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F756" s="19" t="n">
         <f aca="false">F752*F755</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G756" s="19" t="n">
         <f aca="false">G752*G755</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="757" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67337,15 +67337,15 @@
       </c>
       <c r="E758" s="19" t="n">
         <f aca="false">E756*(1-E757)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F758" s="19" t="n">
         <f aca="false">F756*(1-F757)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G758" s="19" t="n">
         <f aca="false">G756*(1-G757)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="759" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67534,7 +67534,7 @@
       </c>
       <c r="E766" s="15" t="n">
         <f aca="false">E765/D765-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F766" s="15" t="n">
         <f aca="false">F765/E765-1</f>
@@ -67562,11 +67562,11 @@
       </c>
       <c r="E767" s="15" t="n">
         <f aca="false">E758/E765</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F767" s="15" t="n">
         <f aca="false">F758/F765</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G767" s="15" t="n">
         <f aca="false">G758/G765</f>
@@ -67594,7 +67594,7 @@
       </c>
       <c r="F768" s="15" t="n">
         <f aca="false">(F758+F760)/F765</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G768" s="15" t="n">
         <f aca="false">(G758+G760)/G765</f>
@@ -67614,7 +67614,7 @@
       </c>
       <c r="E769" s="16" t="n">
         <f aca="false">E758/fx/E749</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F769" s="16" t="n">
         <f aca="false">F758/fx/F749</f>
@@ -67622,7 +67622,7 @@
       </c>
       <c r="G769" s="16" t="n">
         <f aca="false">G758/fx/G749</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="770" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67638,11 +67638,11 @@
       </c>
       <c r="E770" s="19" t="n">
         <f aca="false">E756/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F770" s="19" t="n">
         <f aca="false">F756/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G770" s="19" t="n">
         <f aca="false">G756/fx/odm_vr</f>
@@ -67693,7 +67693,7 @@
       </c>
       <c r="G773" s="22" t="n">
         <f aca="false">($D$772+d_ai+vrd_lo)*G756*(1-G757*(1-keep))</f>
-        <v>444.360538667613</v>
+        <v>444.360538667614</v>
       </c>
       <c r="H773" s="4" t="s">
         <v>472</v>
@@ -67720,7 +67720,7 @@
       </c>
       <c r="F774" s="19" t="n">
         <f aca="false">$D$772*F764+F773</f>
-        <v>930.428389330048</v>
+        <v>930.428389330049</v>
       </c>
       <c r="G774" s="19" t="n">
         <f aca="false">$D$772*G764+G773</f>
@@ -67855,15 +67855,15 @@
       </c>
       <c r="E779" s="19" t="n">
         <f aca="false">E774-E778</f>
-        <v>548.458947802378</v>
+        <v>548.458947802379</v>
       </c>
       <c r="F779" s="19" t="n">
         <f aca="false">F774-F778</f>
-        <v>643.517634593937</v>
+        <v>643.517634593938</v>
       </c>
       <c r="G779" s="19" t="n">
         <f aca="false">G774-G778</f>
-        <v>689.336194780446</v>
+        <v>689.336194780447</v>
       </c>
     </row>
     <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67887,7 +67887,7 @@
       </c>
       <c r="F780" s="14" t="n">
         <f aca="false">F779/F765</f>
-        <v>0.0435460585256667</v>
+        <v>0.0435460585256668</v>
       </c>
       <c r="G780" s="14" t="n">
         <f aca="false">G779/G765</f>
@@ -68003,7 +68003,7 @@
       </c>
       <c r="G784" s="22" t="n">
         <f aca="false">G782/G783</f>
-        <v>32.4579473330598</v>
+        <v>32.4579473330599</v>
       </c>
     </row>
     <row r="785" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68019,7 +68019,7 @@
       </c>
       <c r="E785" s="15" t="n">
         <f aca="false">E784/D784-1</f>
-        <v>0.315072062392691</v>
+        <v>0.315072062392692</v>
       </c>
       <c r="F785" s="15" t="n">
         <f aca="false">F784/E784-1</f>
@@ -68075,7 +68075,7 @@
       </c>
       <c r="D791" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E791" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -68174,7 +68174,7 @@
       </c>
       <c r="D795" s="19" t="n">
         <f aca="false">D793*D794</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E795" s="19" t="n">
         <f aca="false">E793*E794</f>
@@ -68198,7 +68198,7 @@
       </c>
       <c r="D796" s="19" t="n">
         <f aca="false">D795*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E796" s="19" t="n">
         <f aca="false">E795*fx</f>
@@ -68289,15 +68289,15 @@
       </c>
       <c r="E800" s="19" t="n">
         <f aca="false">E796*E799</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F800" s="19" t="n">
         <f aca="false">F796*F799</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G800" s="19" t="n">
         <f aca="false">G796*G799</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="801" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68344,15 +68344,15 @@
       </c>
       <c r="E802" s="19" t="n">
         <f aca="false">E800*(1-E801)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F802" s="19" t="n">
         <f aca="false">F800*(1-F801)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G802" s="19" t="n">
         <f aca="false">G800*(1-G801)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="803" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68541,7 +68541,7 @@
       </c>
       <c r="E810" s="15" t="n">
         <f aca="false">E809/D809-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F810" s="15" t="n">
         <f aca="false">F809/E809-1</f>
@@ -68569,11 +68569,11 @@
       </c>
       <c r="E811" s="15" t="n">
         <f aca="false">E802/E809</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F811" s="15" t="n">
         <f aca="false">F802/F809</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G811" s="15" t="n">
         <f aca="false">G802/G809</f>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="F812" s="15" t="n">
         <f aca="false">(F802+F804)/F809</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G812" s="15" t="n">
         <f aca="false">(G802+G804)/G809</f>
@@ -68621,7 +68621,7 @@
       </c>
       <c r="E813" s="16" t="n">
         <f aca="false">E802/fx/E793</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F813" s="16" t="n">
         <f aca="false">F802/fx/F793</f>
@@ -68629,7 +68629,7 @@
       </c>
       <c r="G813" s="16" t="n">
         <f aca="false">G802/fx/G793</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="814" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68645,11 +68645,11 @@
       </c>
       <c r="E814" s="19" t="n">
         <f aca="false">E800/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F814" s="19" t="n">
         <f aca="false">F800/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G814" s="19" t="n">
         <f aca="false">G800/fx/odm_vr</f>
@@ -68700,7 +68700,7 @@
       </c>
       <c r="G817" s="22" t="n">
         <f aca="false">($D$816+d_ai+vrd_hi)*G800*(1-G801*(1-keep))</f>
-        <v>486.924684521436</v>
+        <v>486.924684521437</v>
       </c>
       <c r="H817" s="4" t="s">
         <v>472</v>
@@ -68723,11 +68723,11 @@
       </c>
       <c r="E818" s="19" t="n">
         <f aca="false">$D$816*E808+E817</f>
-        <v>858.416473935085</v>
+        <v>858.416473935086</v>
       </c>
       <c r="F818" s="19" t="n">
         <f aca="false">$D$816*F808+F817</f>
-        <v>969.961207559261</v>
+        <v>969.961207559262</v>
       </c>
       <c r="G818" s="19" t="n">
         <f aca="false">$D$816*G808+G817</f>
@@ -68866,11 +68866,11 @@
       </c>
       <c r="F823" s="19" t="n">
         <f aca="false">F818-F822</f>
-        <v>683.05045282315</v>
+        <v>683.050452823151</v>
       </c>
       <c r="G823" s="19" t="n">
         <f aca="false">G818-G822</f>
-        <v>731.900340634269</v>
+        <v>731.90034063427</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68890,7 +68890,7 @@
       </c>
       <c r="E824" s="14" t="n">
         <f aca="false">E823/E809</f>
-        <v>0.0422257238991703</v>
+        <v>0.0422257238991704</v>
       </c>
       <c r="F824" s="14" t="n">
         <f aca="false">F823/F809</f>
@@ -68946,15 +68946,15 @@
       </c>
       <c r="E826" s="19" t="n">
         <f aca="false">E823*E825</f>
-        <v>382.776178703264</v>
+        <v>382.776178703265</v>
       </c>
       <c r="F826" s="19" t="n">
         <f aca="false">F823*F825</f>
-        <v>450.813298863279</v>
+        <v>450.81329886328</v>
       </c>
       <c r="G826" s="19" t="n">
         <f aca="false">G823*G825</f>
-        <v>483.054224818617</v>
+        <v>483.054224818618</v>
       </c>
     </row>
     <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69026,7 +69026,7 @@
       </c>
       <c r="E829" s="15" t="n">
         <f aca="false">E828/D828-1</f>
-        <v>0.390613344013735</v>
+        <v>0.390613344013736</v>
       </c>
       <c r="F829" s="15" t="n">
         <f aca="false">F828/E828-1</f>
@@ -69082,7 +69082,7 @@
       </c>
       <c r="D835" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E835" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -69181,7 +69181,7 @@
       </c>
       <c r="D839" s="19" t="n">
         <f aca="false">D837*D838</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E839" s="19" t="n">
         <f aca="false">E837*E838</f>
@@ -69205,7 +69205,7 @@
       </c>
       <c r="D840" s="19" t="n">
         <f aca="false">D839*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E840" s="19" t="n">
         <f aca="false">E839*fx</f>
@@ -69296,15 +69296,15 @@
       </c>
       <c r="E844" s="19" t="n">
         <f aca="false">E840*E843</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F844" s="19" t="n">
         <f aca="false">F840*F843</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G844" s="19" t="n">
         <f aca="false">G840*G843</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="845" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69351,15 +69351,15 @@
       </c>
       <c r="E846" s="19" t="n">
         <f aca="false">E844*(1-E845)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F846" s="19" t="n">
         <f aca="false">F844*(1-F845)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G846" s="19" t="n">
         <f aca="false">G844*(1-G845)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="847" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69548,7 +69548,7 @@
       </c>
       <c r="E854" s="15" t="n">
         <f aca="false">E853/D853-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F854" s="15" t="n">
         <f aca="false">F853/E853-1</f>
@@ -69576,11 +69576,11 @@
       </c>
       <c r="E855" s="15" t="n">
         <f aca="false">E846/E853</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F855" s="15" t="n">
         <f aca="false">F846/F853</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G855" s="15" t="n">
         <f aca="false">G846/G853</f>
@@ -69608,7 +69608,7 @@
       </c>
       <c r="F856" s="15" t="n">
         <f aca="false">(F846+F848)/F853</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G856" s="15" t="n">
         <f aca="false">(G846+G848)/G853</f>
@@ -69628,7 +69628,7 @@
       </c>
       <c r="E857" s="16" t="n">
         <f aca="false">E846/fx/E837</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F857" s="16" t="n">
         <f aca="false">F846/fx/F837</f>
@@ -69636,7 +69636,7 @@
       </c>
       <c r="G857" s="16" t="n">
         <f aca="false">G846/fx/G837</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="858" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69652,11 +69652,11 @@
       </c>
       <c r="E858" s="19" t="n">
         <f aca="false">E844/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F858" s="19" t="n">
         <f aca="false">F844/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G858" s="19" t="n">
         <f aca="false">G844/fx/odm_vr</f>
@@ -69703,11 +69703,11 @@
       </c>
       <c r="F861" s="22" t="n">
         <f aca="false">($D$860+d_ai+vrd)*F844*(1-F845*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G861" s="22" t="n">
         <f aca="false">($D$860+d_ai+vrd)*G844*(1-G845*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H861" s="4" t="s">
         <v>472</v>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="F862" s="19" t="n">
         <f aca="false">$D$860*F852+F861</f>
-        <v>954.148080267576</v>
+        <v>954.148080267577</v>
       </c>
       <c r="G862" s="19" t="n">
         <f aca="false">$D$860*G852+G861</f>
@@ -69849,7 +69849,7 @@
       </c>
       <c r="G866" s="19" t="n">
         <f aca="false">G865+opx_adj_hi*G853</f>
-        <v>320.058028696159</v>
+        <v>320.05802869616</v>
       </c>
     </row>
     <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69869,11 +69869,11 @@
       </c>
       <c r="E867" s="19" t="n">
         <f aca="false">E862-E866</f>
-        <v>539.892227032835</v>
+        <v>539.892227032836</v>
       </c>
       <c r="F867" s="19" t="n">
         <f aca="false">F862-F866</f>
-        <v>637.68160194217</v>
+        <v>637.681601942171</v>
       </c>
       <c r="G867" s="19" t="n">
         <f aca="false">G862-G866</f>
@@ -69953,11 +69953,11 @@
       </c>
       <c r="E870" s="19" t="n">
         <f aca="false">E867*E869</f>
-        <v>356.328869841671</v>
+        <v>356.328869841672</v>
       </c>
       <c r="F870" s="19" t="n">
         <f aca="false">F867*F869</f>
-        <v>420.869857281832</v>
+        <v>420.869857281833</v>
       </c>
       <c r="G870" s="19" t="n">
         <f aca="false">G867*G869</f>
@@ -70033,7 +70033,7 @@
       </c>
       <c r="E873" s="15" t="n">
         <f aca="false">E872/D872-1</f>
-        <v>0.294531135500193</v>
+        <v>0.294531135500194</v>
       </c>
       <c r="F873" s="15" t="n">
         <f aca="false">F872/E872-1</f>
@@ -70089,7 +70089,7 @@
       </c>
       <c r="D879" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E879" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -70188,7 +70188,7 @@
       </c>
       <c r="D883" s="19" t="n">
         <f aca="false">D881*D882</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E883" s="19" t="n">
         <f aca="false">E881*E882</f>
@@ -70212,7 +70212,7 @@
       </c>
       <c r="D884" s="19" t="n">
         <f aca="false">D883*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E884" s="19" t="n">
         <f aca="false">E883*fx</f>
@@ -70303,15 +70303,15 @@
       </c>
       <c r="E888" s="19" t="n">
         <f aca="false">E884*E887</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F888" s="19" t="n">
         <f aca="false">F884*F887</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G888" s="19" t="n">
         <f aca="false">G884*G887</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="889" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70358,15 +70358,15 @@
       </c>
       <c r="E890" s="19" t="n">
         <f aca="false">E888*(1-E889)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F890" s="19" t="n">
         <f aca="false">F888*(1-F889)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G890" s="19" t="n">
         <f aca="false">G888*(1-G889)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="891" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70555,7 +70555,7 @@
       </c>
       <c r="E898" s="15" t="n">
         <f aca="false">E897/D897-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F898" s="15" t="n">
         <f aca="false">F897/E897-1</f>
@@ -70583,11 +70583,11 @@
       </c>
       <c r="E899" s="15" t="n">
         <f aca="false">E890/E897</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F899" s="15" t="n">
         <f aca="false">F890/F897</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G899" s="15" t="n">
         <f aca="false">G890/G897</f>
@@ -70615,7 +70615,7 @@
       </c>
       <c r="F900" s="15" t="n">
         <f aca="false">(F890+F892)/F897</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G900" s="15" t="n">
         <f aca="false">(G890+G892)/G897</f>
@@ -70635,7 +70635,7 @@
       </c>
       <c r="E901" s="16" t="n">
         <f aca="false">E890/fx/E881</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F901" s="16" t="n">
         <f aca="false">F890/fx/F881</f>
@@ -70643,7 +70643,7 @@
       </c>
       <c r="G901" s="16" t="n">
         <f aca="false">G890/fx/G881</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70659,11 +70659,11 @@
       </c>
       <c r="E902" s="19" t="n">
         <f aca="false">E888/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F902" s="19" t="n">
         <f aca="false">F888/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G902" s="19" t="n">
         <f aca="false">G888/fx/odm_vr</f>
@@ -70710,11 +70710,11 @@
       </c>
       <c r="F905" s="22" t="n">
         <f aca="false">($D$904+d_ai+vrd)*F888*(1-F889*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G905" s="22" t="n">
         <f aca="false">($D$904+d_ai+vrd)*G888*(1-G889*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H905" s="4" t="s">
         <v>472</v>
@@ -70741,7 +70741,7 @@
       </c>
       <c r="F906" s="19" t="n">
         <f aca="false">$D$904*F896+F905</f>
-        <v>954.148080267576</v>
+        <v>954.148080267577</v>
       </c>
       <c r="G906" s="19" t="n">
         <f aca="false">$D$904*G896+G905</f>
@@ -70876,15 +70876,15 @@
       </c>
       <c r="E911" s="19" t="n">
         <f aca="false">E906-E910</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F911" s="19" t="n">
         <f aca="false">F906-F910</f>
-        <v>667.237325531465</v>
+        <v>667.237325531466</v>
       </c>
       <c r="G911" s="19" t="n">
         <f aca="false">G906-G910</f>
-        <v>714.87468229274</v>
+        <v>714.874682292741</v>
       </c>
     </row>
     <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71040,11 +71040,11 @@
       </c>
       <c r="E917" s="15" t="n">
         <f aca="false">E916/D916-1</f>
-        <v>0.236724392150288</v>
+        <v>0.236724392150289</v>
       </c>
       <c r="F917" s="15" t="n">
         <f aca="false">F916/E916-1</f>
-        <v>0.176034728479648</v>
+        <v>0.176034728479647</v>
       </c>
       <c r="G917" s="15" t="n">
         <f aca="false">G916/F916-1</f>
@@ -71096,7 +71096,7 @@
       </c>
       <c r="D923" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E923" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -71195,7 +71195,7 @@
       </c>
       <c r="D927" s="19" t="n">
         <f aca="false">D925*D926</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E927" s="19" t="n">
         <f aca="false">E925*E926</f>
@@ -71219,7 +71219,7 @@
       </c>
       <c r="D928" s="19" t="n">
         <f aca="false">D927*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E928" s="19" t="n">
         <f aca="false">E927*fx</f>
@@ -71310,15 +71310,15 @@
       </c>
       <c r="E932" s="19" t="n">
         <f aca="false">E928*E931</f>
-        <v>6364.63824722819</v>
+        <v>6364.6382472282</v>
       </c>
       <c r="F932" s="19" t="n">
         <f aca="false">F928*F931</f>
-        <v>8067.92208759445</v>
+        <v>8067.92208759447</v>
       </c>
       <c r="G932" s="19" t="n">
         <f aca="false">G928*G931</f>
-        <v>8731.10684180972</v>
+        <v>8731.10684180974</v>
       </c>
     </row>
     <row r="933" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71365,15 +71365,15 @@
       </c>
       <c r="E934" s="19" t="n">
         <f aca="false">E932*(1-E933)</f>
-        <v>5728.17442250537</v>
+        <v>5728.17442250538</v>
       </c>
       <c r="F934" s="19" t="n">
         <f aca="false">F932*(1-F933)</f>
-        <v>6454.33767007556</v>
+        <v>6454.33767007557</v>
       </c>
       <c r="G934" s="19" t="n">
         <f aca="false">G932*(1-G933)</f>
-        <v>6548.33013135729</v>
+        <v>6548.3301313573</v>
       </c>
     </row>
     <row r="935" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71562,7 +71562,7 @@
       </c>
       <c r="E942" s="15" t="n">
         <f aca="false">E941/D941-1</f>
-        <v>0.231743753385348</v>
+        <v>0.231743753385349</v>
       </c>
       <c r="F942" s="15" t="n">
         <f aca="false">F941/E941-1</f>
@@ -71590,11 +71590,11 @@
       </c>
       <c r="E943" s="15" t="n">
         <f aca="false">E934/E941</f>
-        <v>0.417054076364077</v>
+        <v>0.417054076364078</v>
       </c>
       <c r="F943" s="15" t="n">
         <f aca="false">F934/F941</f>
-        <v>0.43675720884149</v>
+        <v>0.436757208841491</v>
       </c>
       <c r="G943" s="15" t="n">
         <f aca="false">G934/G941</f>
@@ -71622,7 +71622,7 @@
       </c>
       <c r="F944" s="15" t="n">
         <f aca="false">(F934+F936)/F941</f>
-        <v>0.630252113558197</v>
+        <v>0.630252113558198</v>
       </c>
       <c r="G944" s="15" t="n">
         <f aca="false">(G934+G936)/G941</f>
@@ -71642,7 +71642,7 @@
       </c>
       <c r="E945" s="16" t="n">
         <f aca="false">E934/fx/E925</f>
-        <v>4.29818371613544</v>
+        <v>4.29818371613545</v>
       </c>
       <c r="F945" s="16" t="n">
         <f aca="false">F934/fx/F925</f>
@@ -71650,7 +71650,7 @@
       </c>
       <c r="G945" s="16" t="n">
         <f aca="false">G934/fx/G925</f>
-        <v>3.40272877527389</v>
+        <v>3.4027287752739</v>
       </c>
     </row>
     <row r="946" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71666,11 +71666,11 @@
       </c>
       <c r="E946" s="19" t="n">
         <f aca="false">E932/fx/odm_vr</f>
-        <v>29.4659178112416</v>
+        <v>29.4659178112417</v>
       </c>
       <c r="F946" s="19" t="n">
         <f aca="false">F932/fx/odm_vr</f>
-        <v>37.3514911462706</v>
+        <v>37.3514911462707</v>
       </c>
       <c r="G946" s="19" t="n">
         <f aca="false">G932/fx/odm_vr</f>
@@ -71717,11 +71717,11 @@
       </c>
       <c r="F949" s="22" t="n">
         <f aca="false">($D$948+d_ai+vrd)*F932*(1-F933*(1-keep))</f>
-        <v>436.433820423678</v>
+        <v>436.433820423679</v>
       </c>
       <c r="G949" s="22" t="n">
         <f aca="false">($D$948+d_ai+vrd)*G932*(1-G933*(1-keep))</f>
-        <v>469.899026179907</v>
+        <v>469.899026179908</v>
       </c>
       <c r="H949" s="4" t="s">
         <v>472</v>
@@ -71748,7 +71748,7 @@
       </c>
       <c r="F950" s="19" t="n">
         <f aca="false">$D$948*F940+F949</f>
-        <v>954.148080267576</v>
+        <v>954.148080267577</v>
       </c>
       <c r="G950" s="19" t="n">
         <f aca="false">$D$948*G940+G949</f>
@@ -71883,15 +71883,15 @@
       </c>
       <c r="E955" s="19" t="n">
         <f aca="false">E950-E954</f>
-        <v>567.361923396646</v>
+        <v>567.361923396647</v>
       </c>
       <c r="F955" s="19" t="n">
         <f aca="false">F950-F954</f>
-        <v>667.237325531465</v>
+        <v>667.237325531466</v>
       </c>
       <c r="G955" s="19" t="n">
         <f aca="false">G950-G954</f>
-        <v>714.87468229274</v>
+        <v>714.874682292741</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71975,7 +71975,7 @@
       </c>
       <c r="G958" s="19" t="n">
         <f aca="false">G955*G957</f>
-        <v>521.8585180737</v>
+        <v>521.858518073701</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72027,11 +72027,11 @@
       </c>
       <c r="F960" s="22" t="n">
         <f aca="false">F958/F959</f>
-        <v>34.7495533062313</v>
+        <v>34.7495533062314</v>
       </c>
       <c r="G960" s="22" t="n">
         <f aca="false">G958/G959</f>
-        <v>37.2304949514328</v>
+        <v>37.2304949514329</v>
       </c>
     </row>
     <row r="961" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72047,11 +72047,11 @@
       </c>
       <c r="E961" s="15" t="n">
         <f aca="false">E960/D960-1</f>
-        <v>0.504681343782851</v>
+        <v>0.504681343782852</v>
       </c>
       <c r="F961" s="15" t="n">
         <f aca="false">F960/E960-1</f>
-        <v>0.176034728479648</v>
+        <v>0.176034728479647</v>
       </c>
       <c r="G961" s="15" t="n">
         <f aca="false">G960/F960-1</f>
@@ -72092,7 +72092,7 @@
       </c>
       <c r="C966" s="28" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>290.30634608678</v>
+        <v>290.306346086781</v>
       </c>
       <c r="D966" s="28" t="n">
         <f aca="false">Val!B116</f>
@@ -72100,7 +72100,7 @@
       </c>
       <c r="E966" s="28" t="n">
         <f aca="false">tp_w_dcf*C966+(1-tp_w_dcf)*D966</f>
-        <v>349.917288066706</v>
+        <v>349.917288066707</v>
       </c>
       <c r="F966" s="15" t="n">
         <f aca="false">E966/E$966-1</f>
@@ -72148,7 +72148,7 @@
       </c>
       <c r="E968" s="28" t="n">
         <f aca="false">tp_w_dcf*C968+(1-tp_w_dcf)*D968</f>
-        <v>377.089998117929</v>
+        <v>377.08999811793</v>
       </c>
       <c r="F968" s="15" t="n">
         <f aca="false">E968/E$966-1</f>
@@ -72212,7 +72212,7 @@
       </c>
       <c r="C971" s="28" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>290.30634608678</v>
+        <v>290.306346086781</v>
       </c>
       <c r="D971" s="28" t="n">
         <f aca="false">Val!B116</f>
@@ -72220,7 +72220,7 @@
       </c>
       <c r="E971" s="28" t="n">
         <f aca="false">0.4*C971+(1-0.4)*D971</f>
-        <v>361.839476462691</v>
+        <v>361.839476462692</v>
       </c>
       <c r="F971" s="15" t="n">
         <f aca="false">E971/E$966-1</f>
@@ -72236,7 +72236,7 @@
       </c>
       <c r="C972" s="28" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>290.30634608678</v>
+        <v>290.306346086781</v>
       </c>
       <c r="D972" s="28" t="n">
         <f aca="false">Val!B116</f>
@@ -72244,7 +72244,7 @@
       </c>
       <c r="E972" s="28" t="n">
         <f aca="false">0.8*C972+(1-0.8)*D972</f>
-        <v>314.15072287875</v>
+        <v>314.150722878751</v>
       </c>
       <c r="F972" s="15" t="n">
         <f aca="false">E972/E$966-1</f>

--- a/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
+++ b/foxconn/dist/20261025_鴻海模型_v0.2.1.xlsx
@@ -7327,26 +7327,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7545,26 +7545,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7666,26 +7666,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7787,26 +7787,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7908,26 +7908,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8029,26 +8029,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
